--- a/resources/report/60/95/ex_imp/TID_111_VAT INVOICE_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_111_VAT INVOICE_IMP.xlsx
@@ -1748,9 +1748,6 @@
     <xf numFmtId="0" fontId="9" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1837,6 +1834,109 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="48" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1849,9 +1949,6 @@
     <xf numFmtId="0" fontId="34" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1879,106 +1976,9 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -2351,22 +2351,22 @@
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
-      <c r="F2" s="104" t="s">
+      <c r="F2" s="137" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="104"/>
-      <c r="M2" s="104"/>
-      <c r="N2" s="99" t="s">
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="137"/>
+      <c r="N2" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="132"/>
       <c r="R2" s="36"/>
       <c r="S2" s="11"/>
     </row>
@@ -2376,22 +2376,22 @@
       <c r="C3" s="38"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
-      <c r="F3" s="105" t="s">
+      <c r="F3" s="138" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="105"/>
-      <c r="M3" s="105"/>
-      <c r="N3" s="100" t="s">
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="133" t="s">
         <v>48</v>
       </c>
-      <c r="O3" s="100"/>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="133"/>
+      <c r="Q3" s="133"/>
       <c r="R3" s="39"/>
       <c r="S3" s="12"/>
     </row>
@@ -2401,14 +2401,14 @@
       <c r="C4" s="38"/>
       <c r="D4" s="38"/>
       <c r="E4" s="38"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
-      <c r="I4" s="133"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="133"/>
-      <c r="M4" s="133"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
       <c r="N4" s="40"/>
       <c r="O4" s="40"/>
       <c r="P4" s="40"/>
@@ -2422,15 +2422,15 @@
       <c r="C5" s="38"/>
       <c r="D5" s="38"/>
       <c r="E5" s="38"/>
-      <c r="F5" s="103" t="s">
+      <c r="F5" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="103"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
       <c r="M5" s="40"/>
       <c r="N5" s="40"/>
       <c r="O5" s="40"/>
@@ -2464,20 +2464,20 @@
       <c r="A7" s="37"/>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
-      <c r="D7" s="101" t="s">
+      <c r="D7" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="135"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="135"/>
+      <c r="L7" s="135"/>
+      <c r="M7" s="135"/>
+      <c r="N7" s="135"/>
+      <c r="O7" s="135"/>
       <c r="P7" s="38"/>
       <c r="Q7" s="38"/>
       <c r="R7" s="38"/>
@@ -2514,19 +2514,19 @@
       <c r="E9" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="106"/>
-      <c r="K9" s="106"/>
-      <c r="L9" s="106"/>
-      <c r="M9" s="106"/>
-      <c r="N9" s="106"/>
-      <c r="O9" s="106"/>
-      <c r="P9" s="106"/>
-      <c r="Q9" s="106"/>
-      <c r="R9" s="106"/>
+      <c r="F9" s="139"/>
+      <c r="G9" s="139"/>
+      <c r="H9" s="139"/>
+      <c r="I9" s="139"/>
+      <c r="J9" s="139"/>
+      <c r="K9" s="139"/>
+      <c r="L9" s="139"/>
+      <c r="M9" s="139"/>
+      <c r="N9" s="139"/>
+      <c r="O9" s="139"/>
+      <c r="P9" s="139"/>
+      <c r="Q9" s="139"/>
+      <c r="R9" s="139"/>
       <c r="S9" s="14"/>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2539,19 +2539,19 @@
       <c r="E10" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="107"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="107"/>
-      <c r="I10" s="107"/>
-      <c r="J10" s="107"/>
-      <c r="K10" s="107"/>
-      <c r="L10" s="107"/>
-      <c r="M10" s="107"/>
-      <c r="N10" s="107"/>
-      <c r="O10" s="107"/>
-      <c r="P10" s="107"/>
-      <c r="Q10" s="107"/>
-      <c r="R10" s="107"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="140"/>
+      <c r="N10" s="140"/>
+      <c r="O10" s="140"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="140"/>
+      <c r="R10" s="140"/>
       <c r="S10" s="12"/>
     </row>
     <row r="11" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2564,19 +2564,19 @@
       <c r="E11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="98"/>
-      <c r="M11" s="98"/>
-      <c r="N11" s="98"/>
-      <c r="O11" s="98"/>
-      <c r="P11" s="98"/>
-      <c r="Q11" s="98"/>
-      <c r="R11" s="98"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="108"/>
+      <c r="H11" s="108"/>
+      <c r="I11" s="108"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
+      <c r="N11" s="108"/>
+      <c r="O11" s="108"/>
+      <c r="P11" s="108"/>
+      <c r="Q11" s="108"/>
+      <c r="R11" s="108"/>
       <c r="S11" s="12"/>
     </row>
     <row r="12" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2589,11 +2589,11 @@
       <c r="E12" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="124"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="124"/>
       <c r="K12" s="42"/>
       <c r="L12" s="42"/>
       <c r="M12" s="42"/>
@@ -2614,19 +2614,19 @@
       <c r="E13" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="108"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="108"/>
-      <c r="L13" s="108"/>
-      <c r="M13" s="108"/>
-      <c r="N13" s="108"/>
-      <c r="O13" s="108"/>
-      <c r="P13" s="108"/>
-      <c r="Q13" s="108"/>
-      <c r="R13" s="108"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="124"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="124"/>
+      <c r="J13" s="124"/>
+      <c r="K13" s="124"/>
+      <c r="L13" s="124"/>
+      <c r="M13" s="124"/>
+      <c r="N13" s="124"/>
+      <c r="O13" s="124"/>
+      <c r="P13" s="124"/>
+      <c r="Q13" s="124"/>
+      <c r="R13" s="124"/>
       <c r="S13" s="13"/>
     </row>
     <row r="14" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2635,19 +2635,19 @@
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
-      <c r="F14" s="112"/>
-      <c r="G14" s="112"/>
-      <c r="H14" s="112"/>
-      <c r="I14" s="112"/>
-      <c r="J14" s="112"/>
-      <c r="K14" s="112"/>
-      <c r="L14" s="112"/>
-      <c r="M14" s="112"/>
-      <c r="N14" s="112"/>
-      <c r="O14" s="112"/>
-      <c r="P14" s="112"/>
-      <c r="Q14" s="112"/>
-      <c r="R14" s="112"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="125"/>
+      <c r="K14" s="125"/>
+      <c r="L14" s="125"/>
+      <c r="M14" s="125"/>
+      <c r="N14" s="125"/>
+      <c r="O14" s="125"/>
+      <c r="P14" s="125"/>
+      <c r="Q14" s="125"/>
+      <c r="R14" s="125"/>
       <c r="S14" s="13"/>
     </row>
     <row r="15" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2746,21 +2746,21 @@
         <v>41</v>
       </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="98"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="98"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="98"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="98"/>
-      <c r="N19" s="98"/>
-      <c r="O19" s="98"/>
-      <c r="P19" s="98"/>
-      <c r="Q19" s="98"/>
-      <c r="R19" s="98"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="108"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="108"/>
+      <c r="L19" s="108"/>
+      <c r="M19" s="108"/>
+      <c r="N19" s="108"/>
+      <c r="O19" s="108"/>
+      <c r="P19" s="108"/>
+      <c r="Q19" s="108"/>
+      <c r="R19" s="108"/>
       <c r="S19" s="15"/>
     </row>
     <row r="20" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2860,32 +2860,32 @@
       <c r="B24" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="109" t="s">
+      <c r="C24" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="109"/>
-      <c r="I24" s="109"/>
+      <c r="D24" s="126"/>
+      <c r="E24" s="126"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="126"/>
+      <c r="H24" s="126"/>
+      <c r="I24" s="126"/>
       <c r="J24" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="K24" s="109" t="s">
+      <c r="K24" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="109"/>
-      <c r="M24" s="109"/>
-      <c r="N24" s="109" t="s">
+      <c r="L24" s="126"/>
+      <c r="M24" s="126"/>
+      <c r="N24" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="109"/>
-      <c r="P24" s="109"/>
-      <c r="Q24" s="109" t="s">
+      <c r="O24" s="126"/>
+      <c r="P24" s="126"/>
+      <c r="Q24" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="R24" s="109"/>
+      <c r="R24" s="126"/>
       <c r="S24" s="16"/>
     </row>
     <row r="25" spans="1:19" s="4" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2893,32 +2893,32 @@
       <c r="B25" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="110" t="s">
+      <c r="C25" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="110"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="127"/>
       <c r="J25" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="K25" s="110" t="s">
+      <c r="K25" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="L25" s="110"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="110" t="s">
+      <c r="L25" s="127"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="O25" s="110"/>
-      <c r="P25" s="110"/>
-      <c r="Q25" s="110" t="s">
+      <c r="O25" s="127"/>
+      <c r="P25" s="127"/>
+      <c r="Q25" s="127" t="s">
         <v>8</v>
       </c>
-      <c r="R25" s="110"/>
+      <c r="R25" s="127"/>
       <c r="S25" s="17"/>
     </row>
     <row r="26" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2926,243 +2926,243 @@
       <c r="B26" s="61">
         <v>1</v>
       </c>
-      <c r="C26" s="111">
+      <c r="C26" s="123">
         <v>2</v>
       </c>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
+      <c r="D26" s="123"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="123"/>
       <c r="J26" s="61">
         <v>3</v>
       </c>
-      <c r="K26" s="111">
+      <c r="K26" s="123">
         <v>4</v>
       </c>
-      <c r="L26" s="111"/>
-      <c r="M26" s="111"/>
-      <c r="N26" s="111">
+      <c r="L26" s="123"/>
+      <c r="M26" s="123"/>
+      <c r="N26" s="123">
         <v>5</v>
       </c>
-      <c r="O26" s="111"/>
-      <c r="P26" s="111"/>
-      <c r="Q26" s="111" t="s">
+      <c r="O26" s="123"/>
+      <c r="P26" s="123"/>
+      <c r="Q26" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="R26" s="111"/>
+      <c r="R26" s="123"/>
       <c r="S26" s="18"/>
     </row>
     <row r="27" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="62"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="113"/>
-      <c r="D27" s="114"/>
-      <c r="E27" s="114"/>
-      <c r="F27" s="114"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="114"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="64"/>
-      <c r="K27" s="122"/>
-      <c r="L27" s="123"/>
-      <c r="M27" s="124"/>
-      <c r="N27" s="122"/>
-      <c r="O27" s="123"/>
-      <c r="P27" s="124"/>
-      <c r="Q27" s="116"/>
-      <c r="R27" s="117"/>
+      <c r="B27" s="141"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="116"/>
+      <c r="I27" s="117"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="121"/>
+      <c r="M27" s="122"/>
+      <c r="N27" s="120"/>
+      <c r="O27" s="121"/>
+      <c r="P27" s="122"/>
+      <c r="Q27" s="118"/>
+      <c r="R27" s="119"/>
       <c r="S27" s="30"/>
     </row>
     <row r="28" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="62"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="67"/>
-      <c r="G28" s="67"/>
-      <c r="H28" s="67"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="118" t="s">
+      <c r="B28" s="64"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="K28" s="118"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="118"/>
-      <c r="N28" s="118"/>
-      <c r="O28" s="118"/>
-      <c r="P28" s="119"/>
-      <c r="Q28" s="120"/>
-      <c r="R28" s="121"/>
+      <c r="K28" s="111"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="111"/>
+      <c r="N28" s="111"/>
+      <c r="O28" s="111"/>
+      <c r="P28" s="112"/>
+      <c r="Q28" s="106"/>
+      <c r="R28" s="107"/>
       <c r="S28" s="31"/>
     </row>
     <row r="29" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="62"/>
-      <c r="B29" s="127" t="s">
+      <c r="B29" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="128"/>
-      <c r="D29" s="128"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="128"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="118" t="s">
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="111" t="s">
         <v>44</v>
       </c>
-      <c r="K29" s="118"/>
-      <c r="L29" s="118"/>
-      <c r="M29" s="118"/>
-      <c r="N29" s="118"/>
-      <c r="O29" s="118"/>
-      <c r="P29" s="119"/>
-      <c r="Q29" s="120"/>
-      <c r="R29" s="121"/>
+      <c r="K29" s="111"/>
+      <c r="L29" s="111"/>
+      <c r="M29" s="111"/>
+      <c r="N29" s="111"/>
+      <c r="O29" s="111"/>
+      <c r="P29" s="112"/>
+      <c r="Q29" s="106"/>
+      <c r="R29" s="107"/>
       <c r="S29" s="31"/>
     </row>
     <row r="30" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="62"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="118" t="s">
+      <c r="B30" s="69"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="111" t="s">
         <v>45</v>
       </c>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="118"/>
-      <c r="O30" s="118"/>
-      <c r="P30" s="119"/>
-      <c r="Q30" s="120"/>
-      <c r="R30" s="121"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="111"/>
+      <c r="N30" s="111"/>
+      <c r="O30" s="111"/>
+      <c r="P30" s="112"/>
+      <c r="Q30" s="106"/>
+      <c r="R30" s="107"/>
       <c r="S30" s="31"/>
     </row>
-    <row r="31" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" s="6" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="55"/>
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="92" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
       <c r="F31" s="44"/>
-      <c r="G31" s="129"/>
-      <c r="H31" s="129"/>
-      <c r="I31" s="129"/>
-      <c r="J31" s="129"/>
-      <c r="K31" s="129"/>
-      <c r="L31" s="129"/>
-      <c r="M31" s="129"/>
-      <c r="N31" s="129"/>
-      <c r="O31" s="129"/>
-      <c r="P31" s="129"/>
-      <c r="Q31" s="129"/>
-      <c r="R31" s="130"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="113"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="113"/>
+      <c r="M31" s="113"/>
+      <c r="N31" s="113"/>
+      <c r="O31" s="113"/>
+      <c r="P31" s="113"/>
+      <c r="Q31" s="113"/>
+      <c r="R31" s="114"/>
       <c r="S31" s="19"/>
     </row>
-    <row r="32" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="1.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="37"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="73"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="73"/>
-      <c r="K32" s="73"/>
-      <c r="L32" s="73"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="73"/>
-      <c r="O32" s="73"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="73"/>
-      <c r="R32" s="74"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="73"/>
       <c r="S32" s="20"/>
     </row>
     <row r="33" spans="1:19" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="75"/>
-      <c r="B33" s="76"/>
-      <c r="C33" s="136" t="s">
+      <c r="A33" s="74"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="136"/>
-      <c r="E33" s="136"/>
-      <c r="F33" s="136"/>
-      <c r="G33" s="136"/>
-      <c r="H33" s="136"/>
-      <c r="I33" s="136"/>
-      <c r="J33" s="136"/>
-      <c r="K33" s="136"/>
-      <c r="L33" s="136" t="s">
+      <c r="D33" s="101"/>
+      <c r="E33" s="101"/>
+      <c r="F33" s="101"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="101"/>
+      <c r="I33" s="101"/>
+      <c r="J33" s="101"/>
+      <c r="K33" s="101"/>
+      <c r="L33" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="M33" s="136"/>
-      <c r="N33" s="136"/>
-      <c r="O33" s="136"/>
-      <c r="P33" s="136"/>
-      <c r="Q33" s="136"/>
-      <c r="R33" s="136"/>
+      <c r="M33" s="101"/>
+      <c r="N33" s="101"/>
+      <c r="O33" s="101"/>
+      <c r="P33" s="101"/>
+      <c r="Q33" s="101"/>
+      <c r="R33" s="101"/>
       <c r="S33" s="21"/>
     </row>
     <row r="34" spans="1:19" s="8" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="77"/>
-      <c r="B34" s="78"/>
-      <c r="C34" s="126" t="s">
+      <c r="A34" s="76"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="126"/>
-      <c r="E34" s="126"/>
-      <c r="F34" s="126"/>
-      <c r="G34" s="126"/>
-      <c r="H34" s="126"/>
-      <c r="I34" s="126"/>
-      <c r="J34" s="126"/>
-      <c r="K34" s="126"/>
-      <c r="L34" s="126" t="s">
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="102"/>
+      <c r="I34" s="102"/>
+      <c r="J34" s="102"/>
+      <c r="K34" s="102"/>
+      <c r="L34" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="M34" s="126"/>
-      <c r="N34" s="126"/>
-      <c r="O34" s="126"/>
-      <c r="P34" s="126"/>
-      <c r="Q34" s="126"/>
-      <c r="R34" s="126"/>
+      <c r="M34" s="102"/>
+      <c r="N34" s="102"/>
+      <c r="O34" s="102"/>
+      <c r="P34" s="102"/>
+      <c r="Q34" s="102"/>
+      <c r="R34" s="102"/>
       <c r="S34" s="22"/>
     </row>
     <row r="35" spans="1:19" s="9" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="125" t="s">
+      <c r="B35" s="78"/>
+      <c r="C35" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="125"/>
-      <c r="E35" s="125"/>
-      <c r="F35" s="125"/>
-      <c r="G35" s="125"/>
-      <c r="H35" s="125"/>
-      <c r="I35" s="125"/>
-      <c r="J35" s="125"/>
-      <c r="K35" s="125"/>
-      <c r="L35" s="125" t="s">
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="103"/>
+      <c r="J35" s="103"/>
+      <c r="K35" s="103"/>
+      <c r="L35" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="M35" s="125"/>
-      <c r="N35" s="125"/>
-      <c r="O35" s="125"/>
-      <c r="P35" s="125"/>
-      <c r="Q35" s="125"/>
-      <c r="R35" s="125"/>
+      <c r="M35" s="103"/>
+      <c r="N35" s="103"/>
+      <c r="O35" s="103"/>
+      <c r="P35" s="103"/>
+      <c r="Q35" s="103"/>
+      <c r="R35" s="103"/>
       <c r="S35" s="23"/>
     </row>
     <row r="36" spans="1:19" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -3198,43 +3198,43 @@
       <c r="I37" s="42"/>
       <c r="J37" s="42"/>
       <c r="K37" s="38"/>
-      <c r="L37" s="141" t="s">
+      <c r="L37" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="M37" s="80"/>
-      <c r="N37" s="80"/>
-      <c r="O37" s="139"/>
-      <c r="P37" s="139"/>
-      <c r="Q37" s="139"/>
-      <c r="R37" s="140"/>
+      <c r="M37" s="79"/>
+      <c r="N37" s="79"/>
+      <c r="O37" s="94"/>
+      <c r="P37" s="94"/>
+      <c r="Q37" s="94"/>
+      <c r="R37" s="95"/>
       <c r="S37" s="25"/>
     </row>
     <row r="38" spans="1:19" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A38" s="81"/>
-      <c r="B38" s="82"/>
-      <c r="C38" s="82"/>
-      <c r="D38" s="82"/>
-      <c r="E38" s="82"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="82"/>
-      <c r="L38" s="96" t="s">
+      <c r="A38" s="80"/>
+      <c r="B38" s="81"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
+      <c r="K38" s="81"/>
+      <c r="L38" s="130" t="s">
         <v>46</v>
       </c>
-      <c r="M38" s="97"/>
-      <c r="N38" s="97"/>
-      <c r="O38" s="94"/>
-      <c r="P38" s="94"/>
-      <c r="Q38" s="94"/>
-      <c r="R38" s="95"/>
+      <c r="M38" s="131"/>
+      <c r="N38" s="131"/>
+      <c r="O38" s="128"/>
+      <c r="P38" s="128"/>
+      <c r="Q38" s="128"/>
+      <c r="R38" s="129"/>
       <c r="S38" s="26"/>
     </row>
     <row r="39" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="37"/>
-      <c r="B39" s="84"/>
+      <c r="B39" s="83"/>
       <c r="C39" s="38"/>
       <c r="D39" s="38"/>
       <c r="E39" s="38"/>
@@ -3244,23 +3244,23 @@
       <c r="I39" s="42"/>
       <c r="J39" s="42"/>
       <c r="K39" s="38"/>
-      <c r="L39" s="85" t="s">
+      <c r="L39" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="M39" s="86"/>
-      <c r="N39" s="87"/>
-      <c r="O39" s="131"/>
-      <c r="P39" s="131"/>
-      <c r="Q39" s="131"/>
-      <c r="R39" s="132"/>
+      <c r="M39" s="85"/>
+      <c r="N39" s="86"/>
+      <c r="O39" s="96"/>
+      <c r="P39" s="96"/>
+      <c r="Q39" s="96"/>
+      <c r="R39" s="97"/>
       <c r="S39" s="27"/>
     </row>
     <row r="40" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="37"/>
-      <c r="B40" s="88"/>
-      <c r="C40" s="89"/>
-      <c r="D40" s="89"/>
-      <c r="E40" s="89"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="88"/>
+      <c r="D40" s="88"/>
+      <c r="E40" s="88"/>
       <c r="F40" s="42"/>
       <c r="G40" s="42"/>
       <c r="H40" s="42"/>
@@ -3278,19 +3278,19 @@
     </row>
     <row r="41" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="37"/>
-      <c r="B41" s="90" t="s">
+      <c r="B41" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="C41" s="91"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="138"/>
-      <c r="H41" s="138"/>
-      <c r="I41" s="138"/>
-      <c r="J41" s="138"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="105"/>
       <c r="K41" s="38"/>
-      <c r="L41" s="88"/>
+      <c r="L41" s="87"/>
       <c r="M41" s="42"/>
       <c r="N41" s="42"/>
       <c r="O41" s="42"/>
@@ -3301,19 +3301,19 @@
     </row>
     <row r="42" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37"/>
-      <c r="B42" s="137" t="s">
+      <c r="B42" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="137"/>
-      <c r="D42" s="137"/>
-      <c r="E42" s="137"/>
-      <c r="F42" s="137"/>
-      <c r="G42" s="137"/>
-      <c r="H42" s="137"/>
-      <c r="I42" s="137"/>
-      <c r="J42" s="137"/>
-      <c r="K42" s="137"/>
-      <c r="L42" s="88"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="104"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="104"/>
+      <c r="K42" s="104"/>
+      <c r="L42" s="87"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
       <c r="O42" s="42"/>
@@ -3323,53 +3323,95 @@
       <c r="S42" s="24"/>
     </row>
     <row r="43" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="92"/>
-      <c r="B43" s="134" t="s">
+      <c r="A43" s="91"/>
+      <c r="B43" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="134"/>
-      <c r="D43" s="134"/>
-      <c r="E43" s="134"/>
-      <c r="F43" s="134"/>
-      <c r="G43" s="134"/>
-      <c r="H43" s="134"/>
-      <c r="I43" s="134"/>
-      <c r="J43" s="134"/>
-      <c r="K43" s="134"/>
-      <c r="L43" s="134"/>
-      <c r="M43" s="134"/>
-      <c r="N43" s="134"/>
-      <c r="O43" s="134"/>
-      <c r="P43" s="134"/>
-      <c r="Q43" s="134"/>
-      <c r="R43" s="134"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="99"/>
+      <c r="N43" s="99"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="99"/>
+      <c r="R43" s="99"/>
       <c r="S43" s="28"/>
     </row>
     <row r="44" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="38"/>
-      <c r="B44" s="135" t="s">
+      <c r="B44" s="100" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="135"/>
-      <c r="D44" s="135"/>
-      <c r="E44" s="135"/>
-      <c r="F44" s="135"/>
-      <c r="G44" s="135"/>
-      <c r="H44" s="135"/>
-      <c r="I44" s="135"/>
-      <c r="J44" s="135"/>
-      <c r="K44" s="135"/>
-      <c r="L44" s="135"/>
-      <c r="M44" s="135"/>
-      <c r="N44" s="135"/>
-      <c r="O44" s="135"/>
-      <c r="P44" s="135"/>
-      <c r="Q44" s="135"/>
-      <c r="R44" s="135"/>
+      <c r="C44" s="100"/>
+      <c r="D44" s="100"/>
+      <c r="E44" s="100"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="100"/>
+      <c r="H44" s="100"/>
+      <c r="I44" s="100"/>
+      <c r="J44" s="100"/>
+      <c r="K44" s="100"/>
+      <c r="L44" s="100"/>
+      <c r="M44" s="100"/>
+      <c r="N44" s="100"/>
+      <c r="O44" s="100"/>
+      <c r="P44" s="100"/>
+      <c r="Q44" s="100"/>
+      <c r="R44" s="100"/>
       <c r="S44" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="F11:R11"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:O7"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="F3:M3"/>
+    <mergeCell ref="F9:R9"/>
+    <mergeCell ref="F10:R10"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="G31:R31"/>
     <mergeCell ref="O37:R37"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="F4:M4"/>
@@ -3386,48 +3428,6 @@
     <mergeCell ref="H34:K34"/>
     <mergeCell ref="H35:K35"/>
     <mergeCell ref="D19:R19"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="G31:R31"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="F11:R11"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:O7"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="F3:M3"/>
-    <mergeCell ref="F9:R9"/>
-    <mergeCell ref="F10:R10"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q26:R26"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_111_VAT INVOICE_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_111_VAT INVOICE_IMP.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\NODE\einvoicevn.com\resources\report\60\95\ex_imp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\GENUWIN\19. Package\98. 2205 WABOOK\1.2307 WeTAX\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9384"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="9660" windowHeight="5496"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="4" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -355,71 +355,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Ngày /</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Date</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> tháng / </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>month</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">    năm /</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>year</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-  </si>
-  <si>
     <t>VAT INVOICE</t>
   </si>
   <si>
@@ -630,52 +565,101 @@
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
       <t>:</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
+  </si>
+  <si>
+    <r>
+      <t>Số /</t>
+    </r>
+    <r>
+      <rPr>
         <i/>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Số /</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
+      <t>No</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>No</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ngày /</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>:</t>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> tháng / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>month</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">    năm /</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>year</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
     </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="55" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1010,16 +994,14 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color indexed="8"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="8"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1119,7 +1101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1338,6 +1320,30 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1518,6 +1524,32 @@
       <bottom style="medium">
         <color rgb="FF0070C0"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1596,83 +1628,83 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="30" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="32" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1690,7 +1722,7 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1724,52 +1756,43 @@
     <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="16" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="18" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1778,16 +1801,16 @@
     <xf numFmtId="0" fontId="9" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1796,8 +1819,11 @@
     <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1809,15 +1835,15 @@
     <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="48" fillId="18" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1828,29 +1854,100 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="22" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1859,59 +1956,35 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
@@ -1919,65 +1992,20 @@
     <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="16" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="14" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="15" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2302,27 +2330,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S44"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="1.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.5546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="1.6640625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="5.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="1.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.6640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="1.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.33203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="0.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.77734375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.77734375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="4.21875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="0.77734375" style="1" customWidth="1"/>
     <col min="14" max="14" width="5.6640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="4.6640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="0.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="4.77734375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="0.77734375" style="1" customWidth="1"/>
     <col min="17" max="17" width="5.6640625" style="1" customWidth="1"/>
     <col min="18" max="18" width="14.6640625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="1.6640625" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.33203125" style="1"/>
+    <col min="19" max="19" width="1.77734375" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.21875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2345,28 +2374,28 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="32"/>
     </row>
-    <row r="2" spans="1:19" ht="25.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="25.05" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33"/>
       <c r="B2" s="34"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
-      <c r="F2" s="137" t="s">
+      <c r="F2" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="132" t="s">
-        <v>47</v>
-      </c>
-      <c r="O2" s="132"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="132"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="96" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="96"/>
+      <c r="P2" s="96"/>
+      <c r="Q2" s="96"/>
       <c r="R2" s="36"/>
       <c r="S2" s="11"/>
     </row>
@@ -2376,39 +2405,39 @@
       <c r="C3" s="38"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
-      <c r="F3" s="138" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="138"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="138"/>
-      <c r="N3" s="133" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="133"/>
-      <c r="P3" s="133"/>
-      <c r="Q3" s="133"/>
+      <c r="F3" s="102" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" s="97"/>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="97"/>
       <c r="R3" s="39"/>
       <c r="S3" s="12"/>
     </row>
-    <row r="4" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37"/>
       <c r="B4" s="38"/>
       <c r="C4" s="38"/>
       <c r="D4" s="38"/>
       <c r="E4" s="38"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="121"/>
       <c r="N4" s="40"/>
       <c r="O4" s="40"/>
       <c r="P4" s="40"/>
@@ -2422,15 +2451,15 @@
       <c r="C5" s="38"/>
       <c r="D5" s="38"/>
       <c r="E5" s="38"/>
-      <c r="F5" s="136" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
+      <c r="F5" s="100" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
       <c r="M5" s="40"/>
       <c r="N5" s="40"/>
       <c r="O5" s="40"/>
@@ -2464,20 +2493,20 @@
       <c r="A7" s="37"/>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
-      <c r="D7" s="134" t="s">
+      <c r="D7" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="134"/>
-      <c r="F7" s="134"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
-      <c r="M7" s="135"/>
-      <c r="N7" s="135"/>
-      <c r="O7" s="135"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="99"/>
+      <c r="O7" s="99"/>
       <c r="P7" s="38"/>
       <c r="Q7" s="38"/>
       <c r="R7" s="38"/>
@@ -2504,7 +2533,7 @@
       <c r="R8" s="38"/>
       <c r="S8" s="12"/>
     </row>
-    <row r="9" spans="1:19" ht="25.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="25.05" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A9" s="43"/>
       <c r="B9" s="44" t="s">
         <v>28</v>
@@ -2514,19 +2543,19 @@
       <c r="E9" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="139"/>
-      <c r="G9" s="139"/>
-      <c r="H9" s="139"/>
-      <c r="I9" s="139"/>
-      <c r="J9" s="139"/>
-      <c r="K9" s="139"/>
-      <c r="L9" s="139"/>
-      <c r="M9" s="139"/>
-      <c r="N9" s="139"/>
-      <c r="O9" s="139"/>
-      <c r="P9" s="139"/>
-      <c r="Q9" s="139"/>
-      <c r="R9" s="139"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="103"/>
+      <c r="J9" s="103"/>
+      <c r="K9" s="103"/>
+      <c r="L9" s="103"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="103"/>
+      <c r="O9" s="103"/>
+      <c r="P9" s="103"/>
+      <c r="Q9" s="103"/>
+      <c r="R9" s="103"/>
       <c r="S9" s="14"/>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2539,22 +2568,22 @@
       <c r="E10" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="140"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="140"/>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="140"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="104"/>
+      <c r="L10" s="104"/>
+      <c r="M10" s="104"/>
+      <c r="N10" s="104"/>
+      <c r="O10" s="104"/>
+      <c r="P10" s="104"/>
+      <c r="Q10" s="104"/>
+      <c r="R10" s="104"/>
       <c r="S10" s="12"/>
     </row>
-    <row r="11" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37"/>
       <c r="B11" s="41" t="s">
         <v>30</v>
@@ -2564,19 +2593,19 @@
       <c r="E11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="108"/>
-      <c r="G11" s="108"/>
-      <c r="H11" s="108"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="108"/>
-      <c r="M11" s="108"/>
-      <c r="N11" s="108"/>
-      <c r="O11" s="108"/>
-      <c r="P11" s="108"/>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="108"/>
+      <c r="F11" s="95"/>
+      <c r="G11" s="95"/>
+      <c r="H11" s="95"/>
+      <c r="I11" s="95"/>
+      <c r="J11" s="95"/>
+      <c r="K11" s="95"/>
+      <c r="L11" s="95"/>
+      <c r="M11" s="95"/>
+      <c r="N11" s="95"/>
+      <c r="O11" s="95"/>
+      <c r="P11" s="95"/>
+      <c r="Q11" s="95"/>
+      <c r="R11" s="95"/>
       <c r="S11" s="12"/>
     </row>
     <row r="12" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2589,11 +2618,11 @@
       <c r="E12" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="124"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="124"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
       <c r="K12" s="42"/>
       <c r="L12" s="42"/>
       <c r="M12" s="42"/>
@@ -2614,40 +2643,40 @@
       <c r="E13" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="124"/>
-      <c r="G13" s="124"/>
-      <c r="H13" s="124"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="124"/>
-      <c r="K13" s="124"/>
-      <c r="L13" s="124"/>
-      <c r="M13" s="124"/>
-      <c r="N13" s="124"/>
-      <c r="O13" s="124"/>
-      <c r="P13" s="124"/>
-      <c r="Q13" s="124"/>
-      <c r="R13" s="124"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="105"/>
+      <c r="N13" s="105"/>
+      <c r="O13" s="105"/>
+      <c r="P13" s="105"/>
+      <c r="Q13" s="105"/>
+      <c r="R13" s="105"/>
       <c r="S13" s="13"/>
     </row>
-    <row r="14" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37"/>
       <c r="B14" s="38"/>
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="125"/>
-      <c r="K14" s="125"/>
-      <c r="L14" s="125"/>
-      <c r="M14" s="125"/>
-      <c r="N14" s="125"/>
-      <c r="O14" s="125"/>
-      <c r="P14" s="125"/>
-      <c r="Q14" s="125"/>
-      <c r="R14" s="125"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="120"/>
+      <c r="J14" s="120"/>
+      <c r="K14" s="120"/>
+      <c r="L14" s="120"/>
+      <c r="M14" s="120"/>
+      <c r="N14" s="120"/>
+      <c r="O14" s="120"/>
+      <c r="P14" s="120"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="120"/>
       <c r="S14" s="13"/>
     </row>
     <row r="15" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2694,7 +2723,7 @@
       <c r="R16" s="51"/>
       <c r="S16" s="29"/>
     </row>
-    <row r="17" spans="1:19" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="37"/>
       <c r="B17" s="41" t="s">
         <v>27</v>
@@ -2720,7 +2749,7 @@
     <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="37"/>
       <c r="B18" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="41"/>
@@ -2740,27 +2769,27 @@
       <c r="R18" s="53"/>
       <c r="S18" s="15"/>
     </row>
-    <row r="19" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="37"/>
       <c r="B19" s="41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="108"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="108"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="108"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="108"/>
-      <c r="P19" s="108"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="108"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="53"/>
+      <c r="P19" s="53"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="53"/>
       <c r="S19" s="15"/>
     </row>
     <row r="20" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2857,315 +2886,315 @@
     </row>
     <row r="24" spans="1:19" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A24" s="55"/>
-      <c r="B24" s="56" t="s">
+      <c r="B24" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="126" t="s">
+      <c r="C24" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="126"/>
-      <c r="E24" s="126"/>
-      <c r="F24" s="126"/>
-      <c r="G24" s="126"/>
-      <c r="H24" s="126"/>
-      <c r="I24" s="126"/>
-      <c r="J24" s="57" t="s">
+      <c r="D24" s="106"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="106"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="106"/>
+      <c r="I24" s="106"/>
+      <c r="J24" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="K24" s="126" t="s">
+      <c r="K24" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="126"/>
-      <c r="M24" s="126"/>
-      <c r="N24" s="126" t="s">
+      <c r="L24" s="106"/>
+      <c r="M24" s="106"/>
+      <c r="N24" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="126"/>
-      <c r="P24" s="126"/>
-      <c r="Q24" s="126" t="s">
+      <c r="O24" s="106"/>
+      <c r="P24" s="106"/>
+      <c r="Q24" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="R24" s="126"/>
+      <c r="R24" s="106"/>
       <c r="S24" s="16"/>
     </row>
     <row r="25" spans="1:19" s="4" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="58"/>
-      <c r="B25" s="59" t="s">
+      <c r="A25" s="56"/>
+      <c r="B25" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="127" t="s">
+      <c r="C25" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="127"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
-      <c r="J25" s="59" t="s">
+      <c r="D25" s="107"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="107"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="K25" s="127" t="s">
+      <c r="K25" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="L25" s="127"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="127" t="s">
+      <c r="L25" s="107"/>
+      <c r="M25" s="107"/>
+      <c r="N25" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="O25" s="127"/>
-      <c r="P25" s="127"/>
-      <c r="Q25" s="127" t="s">
+      <c r="O25" s="107"/>
+      <c r="P25" s="107"/>
+      <c r="Q25" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="R25" s="127"/>
+      <c r="R25" s="107"/>
       <c r="S25" s="17"/>
     </row>
     <row r="26" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="60"/>
-      <c r="B26" s="61">
+      <c r="A26" s="57"/>
+      <c r="B26" s="58">
         <v>1</v>
       </c>
-      <c r="C26" s="123">
+      <c r="C26" s="108">
         <v>2</v>
       </c>
-      <c r="D26" s="123"/>
-      <c r="E26" s="123"/>
-      <c r="F26" s="123"/>
-      <c r="G26" s="123"/>
-      <c r="H26" s="123"/>
-      <c r="I26" s="123"/>
-      <c r="J26" s="61">
+      <c r="D26" s="108"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="108"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="108"/>
+      <c r="I26" s="108"/>
+      <c r="J26" s="58">
         <v>3</v>
       </c>
-      <c r="K26" s="123">
+      <c r="K26" s="108">
         <v>4</v>
       </c>
-      <c r="L26" s="123"/>
-      <c r="M26" s="123"/>
-      <c r="N26" s="123">
+      <c r="L26" s="108"/>
+      <c r="M26" s="108"/>
+      <c r="N26" s="108">
         <v>5</v>
       </c>
-      <c r="O26" s="123"/>
-      <c r="P26" s="123"/>
-      <c r="Q26" s="123" t="s">
+      <c r="O26" s="108"/>
+      <c r="P26" s="108"/>
+      <c r="Q26" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="R26" s="123"/>
+      <c r="R26" s="108"/>
       <c r="S26" s="18"/>
     </row>
     <row r="27" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="62"/>
-      <c r="B27" s="141"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="117"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="120"/>
-      <c r="L27" s="121"/>
-      <c r="M27" s="122"/>
-      <c r="N27" s="120"/>
-      <c r="O27" s="121"/>
-      <c r="P27" s="122"/>
-      <c r="Q27" s="118"/>
-      <c r="R27" s="119"/>
+      <c r="A27" s="59"/>
+      <c r="B27" s="134"/>
+      <c r="C27" s="109"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="111"/>
+      <c r="J27" s="60"/>
+      <c r="K27" s="135"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="137"/>
+      <c r="N27" s="138"/>
+      <c r="O27" s="139"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="140"/>
+      <c r="R27" s="141"/>
       <c r="S27" s="30"/>
     </row>
     <row r="28" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="62"/>
-      <c r="B28" s="64"/>
-      <c r="C28" s="65"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="111" t="s">
+      <c r="A28" s="59"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="113" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" s="113"/>
+      <c r="L28" s="113"/>
+      <c r="M28" s="113"/>
+      <c r="N28" s="113"/>
+      <c r="O28" s="113"/>
+      <c r="P28" s="114"/>
+      <c r="Q28" s="115"/>
+      <c r="R28" s="116"/>
+      <c r="S28" s="31"/>
+    </row>
+    <row r="29" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="59"/>
+      <c r="B29" s="118" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="64"/>
+      <c r="J29" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="K28" s="111"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="111"/>
-      <c r="N28" s="111"/>
-      <c r="O28" s="111"/>
-      <c r="P28" s="112"/>
-      <c r="Q28" s="106"/>
-      <c r="R28" s="107"/>
-      <c r="S28" s="31"/>
-    </row>
-    <row r="29" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="62"/>
-      <c r="B29" s="109" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
-      <c r="G29" s="67"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="67"/>
-      <c r="J29" s="111" t="s">
+      <c r="K29" s="113"/>
+      <c r="L29" s="113"/>
+      <c r="M29" s="113"/>
+      <c r="N29" s="113"/>
+      <c r="O29" s="113"/>
+      <c r="P29" s="114"/>
+      <c r="Q29" s="115"/>
+      <c r="R29" s="116"/>
+      <c r="S29" s="31"/>
+    </row>
+    <row r="30" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="59"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="K29" s="111"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="111"/>
-      <c r="N29" s="111"/>
-      <c r="O29" s="111"/>
-      <c r="P29" s="112"/>
-      <c r="Q29" s="106"/>
-      <c r="R29" s="107"/>
-      <c r="S29" s="31"/>
-    </row>
-    <row r="30" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="62"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="111" t="s">
-        <v>45</v>
-      </c>
-      <c r="K30" s="111"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="111"/>
-      <c r="N30" s="111"/>
-      <c r="O30" s="111"/>
-      <c r="P30" s="112"/>
-      <c r="Q30" s="106"/>
-      <c r="R30" s="107"/>
+      <c r="K30" s="113"/>
+      <c r="L30" s="113"/>
+      <c r="M30" s="113"/>
+      <c r="N30" s="113"/>
+      <c r="O30" s="113"/>
+      <c r="P30" s="114"/>
+      <c r="Q30" s="115"/>
+      <c r="R30" s="116"/>
       <c r="S30" s="31"/>
     </row>
-    <row r="31" spans="1:19" s="6" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="55"/>
-      <c r="B31" s="92" t="s">
+      <c r="B31" s="131" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
       <c r="F31" s="44"/>
-      <c r="G31" s="113"/>
-      <c r="H31" s="113"/>
-      <c r="I31" s="113"/>
-      <c r="J31" s="113"/>
-      <c r="K31" s="113"/>
-      <c r="L31" s="113"/>
-      <c r="M31" s="113"/>
-      <c r="N31" s="113"/>
-      <c r="O31" s="113"/>
-      <c r="P31" s="113"/>
-      <c r="Q31" s="113"/>
-      <c r="R31" s="114"/>
+      <c r="G31" s="132"/>
+      <c r="H31" s="132"/>
+      <c r="I31" s="132"/>
+      <c r="J31" s="132"/>
+      <c r="K31" s="132"/>
+      <c r="L31" s="132"/>
+      <c r="M31" s="132"/>
+      <c r="N31" s="132"/>
+      <c r="O31" s="132"/>
+      <c r="P31" s="132"/>
+      <c r="Q31" s="132"/>
+      <c r="R31" s="133"/>
       <c r="S31" s="19"/>
     </row>
-    <row r="32" spans="1:19" ht="1.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="37"/>
-      <c r="B32" s="70"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="72"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="72"/>
-      <c r="L32" s="72"/>
-      <c r="M32" s="72"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="72"/>
-      <c r="P32" s="72"/>
-      <c r="Q32" s="72"/>
-      <c r="R32" s="73"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="69"/>
+      <c r="L32" s="69"/>
+      <c r="M32" s="69"/>
+      <c r="N32" s="69"/>
+      <c r="O32" s="69"/>
+      <c r="P32" s="69"/>
+      <c r="Q32" s="69"/>
+      <c r="R32" s="70"/>
       <c r="S32" s="20"/>
     </row>
     <row r="33" spans="1:19" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="74"/>
-      <c r="B33" s="75"/>
-      <c r="C33" s="101" t="s">
+      <c r="A33" s="71"/>
+      <c r="B33" s="72"/>
+      <c r="C33" s="124" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="101"/>
-      <c r="H33" s="101"/>
-      <c r="I33" s="101"/>
-      <c r="J33" s="101"/>
-      <c r="K33" s="101"/>
-      <c r="L33" s="101" t="s">
-        <v>40</v>
-      </c>
-      <c r="M33" s="101"/>
-      <c r="N33" s="101"/>
-      <c r="O33" s="101"/>
-      <c r="P33" s="101"/>
-      <c r="Q33" s="101"/>
-      <c r="R33" s="101"/>
+      <c r="D33" s="124"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="124"/>
+      <c r="G33" s="124"/>
+      <c r="H33" s="124"/>
+      <c r="I33" s="124"/>
+      <c r="J33" s="124"/>
+      <c r="K33" s="124"/>
+      <c r="L33" s="124" t="s">
+        <v>39</v>
+      </c>
+      <c r="M33" s="124"/>
+      <c r="N33" s="124"/>
+      <c r="O33" s="124"/>
+      <c r="P33" s="124"/>
+      <c r="Q33" s="124"/>
+      <c r="R33" s="124"/>
       <c r="S33" s="21"/>
     </row>
     <row r="34" spans="1:19" s="8" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="76"/>
-      <c r="B34" s="77"/>
-      <c r="C34" s="102" t="s">
+      <c r="A34" s="73"/>
+      <c r="B34" s="74"/>
+      <c r="C34" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="102"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="102"/>
-      <c r="H34" s="102"/>
-      <c r="I34" s="102"/>
-      <c r="J34" s="102"/>
-      <c r="K34" s="102"/>
-      <c r="L34" s="102" t="s">
+      <c r="D34" s="117"/>
+      <c r="E34" s="117"/>
+      <c r="F34" s="117"/>
+      <c r="G34" s="117"/>
+      <c r="H34" s="117"/>
+      <c r="I34" s="117"/>
+      <c r="J34" s="117"/>
+      <c r="K34" s="117"/>
+      <c r="L34" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="M34" s="102"/>
-      <c r="N34" s="102"/>
-      <c r="O34" s="102"/>
-      <c r="P34" s="102"/>
-      <c r="Q34" s="102"/>
-      <c r="R34" s="102"/>
+      <c r="M34" s="117"/>
+      <c r="N34" s="117"/>
+      <c r="O34" s="117"/>
+      <c r="P34" s="117"/>
+      <c r="Q34" s="117"/>
+      <c r="R34" s="117"/>
       <c r="S34" s="22"/>
     </row>
     <row r="35" spans="1:19" s="9" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="58"/>
-      <c r="B35" s="78"/>
-      <c r="C35" s="103" t="s">
+      <c r="A35" s="56"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="103"/>
-      <c r="J35" s="103"/>
-      <c r="K35" s="103"/>
-      <c r="L35" s="103" t="s">
+      <c r="D35" s="112"/>
+      <c r="E35" s="112"/>
+      <c r="F35" s="112"/>
+      <c r="G35" s="112"/>
+      <c r="H35" s="112"/>
+      <c r="I35" s="112"/>
+      <c r="J35" s="112"/>
+      <c r="K35" s="112"/>
+      <c r="L35" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="M35" s="103"/>
-      <c r="N35" s="103"/>
-      <c r="O35" s="103"/>
-      <c r="P35" s="103"/>
-      <c r="Q35" s="103"/>
-      <c r="R35" s="103"/>
+      <c r="M35" s="112"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="112"/>
+      <c r="P35" s="112"/>
+      <c r="Q35" s="112"/>
+      <c r="R35" s="112"/>
       <c r="S35" s="23"/>
     </row>
-    <row r="36" spans="1:19" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="37"/>
       <c r="B36" s="42"/>
       <c r="C36" s="42"/>
@@ -3198,15 +3227,15 @@
       <c r="I37" s="42"/>
       <c r="J37" s="42"/>
       <c r="K37" s="38"/>
-      <c r="L37" s="93" t="s">
+      <c r="L37" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="M37" s="79"/>
-      <c r="N37" s="79"/>
-      <c r="O37" s="94"/>
-      <c r="P37" s="94"/>
-      <c r="Q37" s="94"/>
-      <c r="R37" s="95"/>
+      <c r="M37" s="77"/>
+      <c r="N37" s="77"/>
+      <c r="O37" s="77"/>
+      <c r="P37" s="78"/>
+      <c r="Q37" s="78"/>
+      <c r="R37" s="79"/>
       <c r="S37" s="25"/>
     </row>
     <row r="38" spans="1:19" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
@@ -3221,18 +3250,18 @@
       <c r="I38" s="82"/>
       <c r="J38" s="82"/>
       <c r="K38" s="81"/>
-      <c r="L38" s="130" t="s">
-        <v>46</v>
-      </c>
-      <c r="M38" s="131"/>
-      <c r="N38" s="131"/>
+      <c r="L38" s="127" t="s">
+        <v>45</v>
+      </c>
+      <c r="M38" s="128"/>
+      <c r="N38" s="128"/>
       <c r="O38" s="128"/>
       <c r="P38" s="128"/>
       <c r="Q38" s="128"/>
       <c r="R38" s="129"/>
       <c r="S38" s="26"/>
     </row>
-    <row r="39" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="37"/>
       <c r="B39" s="83"/>
       <c r="C39" s="38"/>
@@ -3244,15 +3273,15 @@
       <c r="I39" s="42"/>
       <c r="J39" s="42"/>
       <c r="K39" s="38"/>
-      <c r="L39" s="84" t="s">
+      <c r="L39" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="M39" s="85"/>
-      <c r="N39" s="86"/>
-      <c r="O39" s="96"/>
-      <c r="P39" s="96"/>
-      <c r="Q39" s="96"/>
-      <c r="R39" s="97"/>
+      <c r="M39" s="84"/>
+      <c r="N39" s="85"/>
+      <c r="O39" s="85"/>
+      <c r="P39" s="85"/>
+      <c r="Q39" s="85"/>
+      <c r="R39" s="86"/>
       <c r="S39" s="27"/>
     </row>
     <row r="40" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3276,19 +3305,19 @@
       <c r="R40" s="42"/>
       <c r="S40" s="24"/>
     </row>
-    <row r="41" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="37"/>
       <c r="B41" s="89" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C41" s="90"/>
       <c r="D41" s="90"/>
       <c r="E41" s="90"/>
       <c r="F41" s="90"/>
-      <c r="G41" s="105"/>
-      <c r="H41" s="105"/>
-      <c r="I41" s="105"/>
-      <c r="J41" s="105"/>
+      <c r="G41" s="126"/>
+      <c r="H41" s="126"/>
+      <c r="I41" s="126"/>
+      <c r="J41" s="126"/>
       <c r="K41" s="38"/>
       <c r="L41" s="87"/>
       <c r="M41" s="42"/>
@@ -3299,20 +3328,20 @@
       <c r="R41" s="42"/>
       <c r="S41" s="24"/>
     </row>
-    <row r="42" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37"/>
-      <c r="B42" s="104" t="s">
-        <v>39</v>
-      </c>
-      <c r="C42" s="104"/>
-      <c r="D42" s="104"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="104"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="104"/>
-      <c r="K42" s="104"/>
+      <c r="B42" s="125" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="125"/>
+      <c r="D42" s="125"/>
+      <c r="E42" s="125"/>
+      <c r="F42" s="125"/>
+      <c r="G42" s="125"/>
+      <c r="H42" s="125"/>
+      <c r="I42" s="125"/>
+      <c r="J42" s="125"/>
+      <c r="K42" s="125"/>
       <c r="L42" s="87"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
@@ -3324,54 +3353,96 @@
     </row>
     <row r="43" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="91"/>
-      <c r="B43" s="99" t="s">
+      <c r="B43" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="99"/>
-      <c r="R43" s="99"/>
+      <c r="C43" s="122"/>
+      <c r="D43" s="122"/>
+      <c r="E43" s="122"/>
+      <c r="F43" s="122"/>
+      <c r="G43" s="122"/>
+      <c r="H43" s="122"/>
+      <c r="I43" s="122"/>
+      <c r="J43" s="122"/>
+      <c r="K43" s="122"/>
+      <c r="L43" s="122"/>
+      <c r="M43" s="122"/>
+      <c r="N43" s="122"/>
+      <c r="O43" s="122"/>
+      <c r="P43" s="122"/>
+      <c r="Q43" s="122"/>
+      <c r="R43" s="122"/>
       <c r="S43" s="28"/>
     </row>
     <row r="44" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="38"/>
-      <c r="B44" s="100" t="s">
+      <c r="B44" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="100"/>
-      <c r="D44" s="100"/>
-      <c r="E44" s="100"/>
-      <c r="F44" s="100"/>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="100"/>
-      <c r="N44" s="100"/>
-      <c r="O44" s="100"/>
-      <c r="P44" s="100"/>
-      <c r="Q44" s="100"/>
-      <c r="R44" s="100"/>
+      <c r="C44" s="123"/>
+      <c r="D44" s="123"/>
+      <c r="E44" s="123"/>
+      <c r="F44" s="123"/>
+      <c r="G44" s="123"/>
+      <c r="H44" s="123"/>
+      <c r="I44" s="123"/>
+      <c r="J44" s="123"/>
+      <c r="K44" s="123"/>
+      <c r="L44" s="123"/>
+      <c r="M44" s="123"/>
+      <c r="N44" s="123"/>
+      <c r="O44" s="123"/>
+      <c r="P44" s="123"/>
+      <c r="Q44" s="123"/>
+      <c r="R44" s="123"/>
       <c r="S44" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="L38:N38"/>
+  <mergeCells count="54">
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="F4:M4"/>
+    <mergeCell ref="B43:R43"/>
+    <mergeCell ref="B44:R44"/>
+    <mergeCell ref="L33:R33"/>
+    <mergeCell ref="L34:R34"/>
+    <mergeCell ref="L35:R35"/>
+    <mergeCell ref="L38:R38"/>
+    <mergeCell ref="B42:K42"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="G31:R31"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="F14:H14"/>
     <mergeCell ref="F11:R11"/>
     <mergeCell ref="N2:Q2"/>
     <mergeCell ref="N3:Q3"/>
@@ -3382,52 +3453,6 @@
     <mergeCell ref="F3:M3"/>
     <mergeCell ref="F9:R9"/>
     <mergeCell ref="F10:R10"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="G31:R31"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O39:R39"/>
-    <mergeCell ref="F4:M4"/>
-    <mergeCell ref="B43:R43"/>
-    <mergeCell ref="B44:R44"/>
-    <mergeCell ref="L33:R33"/>
-    <mergeCell ref="L34:R34"/>
-    <mergeCell ref="L35:R35"/>
-    <mergeCell ref="B42:K42"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="D19:R19"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_111_VAT INVOICE_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_111_VAT INVOICE_IMP.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\GENUWIN\19. Package\98. 2205 WABOOK\1.2307 WeTAX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAP-DEV-030\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9660" windowHeight="5496"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="4" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -119,28 +119,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Số tiền viết bằng chữ / </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>In words</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <sz val="12"/>
         <rFont val="Times New Roman"/>
@@ -565,28 +543,40 @@
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
       <t>:</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>Số /</t>
-    </r>
-    <r>
-      <rPr>
+    <r>
+      <rPr>
+        <b/>
         <i/>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Số /</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
       <t>No</t>
     </r>
     <r>
       <rPr>
+        <b/>
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
@@ -596,27 +586,42 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve"> Số tiền viết bằng chữ / </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>In words</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>Ngày /</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Date</t>
-    </r>
-    <r>
-      <rPr>
+        <i/>
         <sz val="11"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
+      <t xml:space="preserve">Date   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -624,7 +629,8 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <i/>
+        <sz val="11"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -632,7 +638,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -640,7 +646,8 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <i/>
+        <sz val="11"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -648,7 +655,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -994,14 +1001,16 @@
       <family val="1"/>
     </font>
     <font>
+      <b/>
+      <i/>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <i/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1101,7 +1110,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1320,30 +1329,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1524,32 +1509,6 @@
       <bottom style="medium">
         <color rgb="FF0070C0"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1596,7 +1555,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1628,47 +1587,390 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="30" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="48" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1676,336 +1978,6 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="32" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="16" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="18" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="22" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="18" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="16" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="14" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="15" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2330,729 +2302,728 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S44"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="1.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="1.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.77734375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.77734375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.21875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="0.77734375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.6640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="4.77734375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="0.77734375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.6640625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="1.77734375" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.21875" style="1"/>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" style="1" customWidth="1"/>
+    <col min="6" max="7" width="5.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="1.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="0.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="4.7109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="0.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="5.7109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="1.7109375" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-    </row>
-    <row r="2" spans="1:19" ht="25.05" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="101" t="s">
+    <row r="1" spans="1:19" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+    </row>
+    <row r="2" spans="1:19" ht="25.15" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="30"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="96" t="s">
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="100" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="11"/>
+    </row>
+    <row r="3" spans="1:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="104"/>
+      <c r="L3" s="104"/>
+      <c r="M3" s="104"/>
+      <c r="N3" s="101" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="96"/>
-      <c r="P2" s="96"/>
-      <c r="Q2" s="96"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="11"/>
-    </row>
-    <row r="3" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="102" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="97" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" s="97"/>
-      <c r="P3" s="97"/>
-      <c r="Q3" s="97"/>
-      <c r="R3" s="39"/>
+      <c r="O3" s="101"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
+      <c r="R3" s="36"/>
       <c r="S3" s="12"/>
     </row>
-    <row r="4" spans="1:19" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="37"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="121"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
+    <row r="4" spans="1:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="34"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="134"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="134"/>
+      <c r="M4" s="134"/>
+      <c r="N4" s="37"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="37"/>
       <c r="S4" s="12"/>
     </row>
-    <row r="5" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="37"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="100" t="s">
+    <row r="5" spans="1:19" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="34"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="141" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="100"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
+      <c r="G5" s="141"/>
+      <c r="H5" s="141"/>
+      <c r="I5" s="141"/>
+      <c r="J5" s="141"/>
+      <c r="K5" s="141"/>
+      <c r="L5" s="141"/>
+      <c r="M5" s="141"/>
+      <c r="N5" s="141"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
       <c r="S5" s="13"/>
     </row>
-    <row r="6" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
+    <row r="6" spans="1:19" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="34"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+      <c r="O6" s="37"/>
+      <c r="P6" s="37"/>
+      <c r="Q6" s="37"/>
+      <c r="R6" s="37"/>
       <c r="S6" s="13"/>
     </row>
-    <row r="7" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="37"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="98" t="s">
+    <row r="7" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="34"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="99"/>
-      <c r="O7" s="99"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="102"/>
+      <c r="O7" s="102"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
       <c r="S7" s="13"/>
     </row>
-    <row r="8" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
+    <row r="8" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="34"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
       <c r="S8" s="12"/>
     </row>
-    <row r="9" spans="1:19" ht="25.05" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43"/>
-      <c r="B9" s="44" t="s">
+    <row r="9" spans="1:19" ht="25.15" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="40"/>
+      <c r="B9" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="105"/>
+      <c r="P9" s="105"/>
+      <c r="Q9" s="105"/>
+      <c r="R9" s="105"/>
+      <c r="S9" s="14"/>
+    </row>
+    <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="34"/>
+      <c r="B10" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="44" t="s">
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="103"/>
-      <c r="L9" s="103"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="103"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="103"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="103"/>
-      <c r="S9" s="14"/>
-    </row>
-    <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
-      <c r="B10" s="41" t="s">
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="106"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="106"/>
+      <c r="N10" s="106"/>
+      <c r="O10" s="106"/>
+      <c r="P10" s="106"/>
+      <c r="Q10" s="106"/>
+      <c r="R10" s="106"/>
+      <c r="S10" s="12"/>
+    </row>
+    <row r="11" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="34"/>
+      <c r="B11" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38" t="s">
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="104"/>
-      <c r="M10" s="104"/>
-      <c r="N10" s="104"/>
-      <c r="O10" s="104"/>
-      <c r="P10" s="104"/>
-      <c r="Q10" s="104"/>
-      <c r="R10" s="104"/>
-      <c r="S10" s="12"/>
-    </row>
-    <row r="11" spans="1:19" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37"/>
-      <c r="B11" s="41" t="s">
+      <c r="F11" s="99"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="99"/>
+      <c r="L11" s="99"/>
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="99"/>
+      <c r="P11" s="99"/>
+      <c r="Q11" s="99"/>
+      <c r="R11" s="99"/>
+      <c r="S11" s="12"/>
+    </row>
+    <row r="12" spans="1:19" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="34"/>
+      <c r="B12" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38" t="s">
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
-      <c r="I11" s="95"/>
-      <c r="J11" s="95"/>
-      <c r="K11" s="95"/>
-      <c r="L11" s="95"/>
-      <c r="M11" s="95"/>
-      <c r="N11" s="95"/>
-      <c r="O11" s="95"/>
-      <c r="P11" s="95"/>
-      <c r="Q11" s="95"/>
-      <c r="R11" s="95"/>
-      <c r="S11" s="12"/>
-    </row>
-    <row r="12" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="37"/>
-      <c r="B12" s="46" t="s">
+      <c r="F12" s="107"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="107"/>
+      <c r="I12" s="107"/>
+      <c r="J12" s="107"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="94"/>
+      <c r="P12" s="93"/>
+      <c r="Q12" s="93"/>
+      <c r="R12" s="93"/>
+      <c r="S12" s="13"/>
+    </row>
+    <row r="13" spans="1:19" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="34"/>
+      <c r="B13" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38" t="s">
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="105"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="13"/>
-    </row>
-    <row r="13" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
-      <c r="B13" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="105"/>
-      <c r="L13" s="105"/>
-      <c r="M13" s="105"/>
-      <c r="N13" s="105"/>
-      <c r="O13" s="105"/>
-      <c r="P13" s="105"/>
-      <c r="Q13" s="105"/>
-      <c r="R13" s="105"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="107"/>
+      <c r="L13" s="107"/>
+      <c r="M13" s="107"/>
+      <c r="N13" s="107"/>
+      <c r="O13" s="107"/>
+      <c r="P13" s="107"/>
+      <c r="Q13" s="107"/>
+      <c r="R13" s="107"/>
       <c r="S13" s="13"/>
     </row>
-    <row r="14" spans="1:19" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="37"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="120"/>
-      <c r="J14" s="120"/>
-      <c r="K14" s="120"/>
-      <c r="L14" s="120"/>
-      <c r="M14" s="120"/>
-      <c r="N14" s="120"/>
-      <c r="O14" s="120"/>
-      <c r="P14" s="120"/>
-      <c r="Q14" s="120"/>
-      <c r="R14" s="120"/>
+    <row r="14" spans="1:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="34"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="111"/>
       <c r="S14" s="13"/>
     </row>
-    <row r="15" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="37"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="49"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="49"/>
-      <c r="R15" s="49"/>
+    <row r="15" spans="1:19" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="34"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
       <c r="S15" s="13"/>
     </row>
-    <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37"/>
-      <c r="B16" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="51"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="51"/>
-      <c r="S16" s="29"/>
-    </row>
-    <row r="17" spans="1:19" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="37"/>
-      <c r="B17" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="52"/>
+    <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="34"/>
+      <c r="B16" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="48"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="48"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="26"/>
+    </row>
+    <row r="17" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="34"/>
+      <c r="B17" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="49"/>
+      <c r="P17" s="49"/>
+      <c r="Q17" s="49"/>
+      <c r="R17" s="49"/>
       <c r="S17" s="15"/>
     </row>
-    <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37"/>
-      <c r="B18" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="53"/>
-      <c r="Q18" s="53"/>
-      <c r="R18" s="53"/>
+    <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="34"/>
+      <c r="B18" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="50"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="50"/>
+      <c r="M18" s="50"/>
+      <c r="N18" s="50"/>
+      <c r="O18" s="50"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="50"/>
+      <c r="R18" s="50"/>
       <c r="S18" s="15"/>
     </row>
-    <row r="19" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="37"/>
-      <c r="B19" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="53"/>
-      <c r="P19" s="53"/>
-      <c r="Q19" s="53"/>
-      <c r="R19" s="53"/>
+    <row r="19" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="34"/>
+      <c r="B19" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="38"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="112"/>
+      <c r="R19" s="112"/>
       <c r="S19" s="15"/>
     </row>
-    <row r="20" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="37"/>
-      <c r="B20" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
+    <row r="20" spans="1:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="34"/>
+      <c r="B20" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="50"/>
+      <c r="M20" s="50"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="50"/>
       <c r="S20" s="15"/>
     </row>
-    <row r="21" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37"/>
-      <c r="B21" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
+    <row r="21" spans="1:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="34"/>
+      <c r="B21" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
       <c r="S21" s="12"/>
     </row>
-    <row r="22" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="37"/>
-      <c r="B22" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="38" t="s">
+    <row r="22" spans="1:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="34"/>
+      <c r="B22" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="38"/>
-      <c r="R22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
       <c r="S22" s="12"/>
     </row>
-    <row r="23" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="37"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="38"/>
+    <row r="23" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="34"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
       <c r="S23" s="12"/>
     </row>
-    <row r="24" spans="1:19" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A24" s="55"/>
-      <c r="B24" s="92" t="s">
+    <row r="24" spans="1:19" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="52"/>
+      <c r="B24" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="106" t="s">
+      <c r="C24" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="106"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="106"/>
-      <c r="I24" s="106"/>
-      <c r="J24" s="93" t="s">
-        <v>34</v>
-      </c>
-      <c r="K24" s="106" t="s">
+      <c r="D24" s="108"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="108"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="108"/>
+      <c r="I24" s="108"/>
+      <c r="J24" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="106"/>
-      <c r="M24" s="106"/>
-      <c r="N24" s="106" t="s">
+      <c r="L24" s="108"/>
+      <c r="M24" s="108"/>
+      <c r="N24" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="106"/>
-      <c r="P24" s="106"/>
-      <c r="Q24" s="106" t="s">
+      <c r="O24" s="108"/>
+      <c r="P24" s="108"/>
+      <c r="Q24" s="108" t="s">
         <v>7</v>
       </c>
-      <c r="R24" s="106"/>
+      <c r="R24" s="108"/>
       <c r="S24" s="16"/>
     </row>
-    <row r="25" spans="1:19" s="4" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="56"/>
-      <c r="B25" s="94" t="s">
+    <row r="25" spans="1:19" s="4" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="55"/>
+      <c r="B25" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="107" t="s">
+      <c r="C25" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="107"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="107"/>
-      <c r="G25" s="107"/>
-      <c r="H25" s="107"/>
-      <c r="I25" s="107"/>
-      <c r="J25" s="94" t="s">
+      <c r="D25" s="109"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="109"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="109"/>
+      <c r="J25" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="K25" s="107" t="s">
+      <c r="K25" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="L25" s="107"/>
-      <c r="M25" s="107"/>
-      <c r="N25" s="107" t="s">
+      <c r="L25" s="109"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="O25" s="107"/>
-      <c r="P25" s="107"/>
-      <c r="Q25" s="107" t="s">
+      <c r="O25" s="109"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="R25" s="107"/>
+      <c r="R25" s="109"/>
       <c r="S25" s="17"/>
     </row>
-    <row r="26" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="57"/>
       <c r="B26" s="58">
         <v>1</v>
       </c>
-      <c r="C26" s="108">
+      <c r="C26" s="110">
         <v>2</v>
       </c>
-      <c r="D26" s="108"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="108"/>
-      <c r="G26" s="108"/>
-      <c r="H26" s="108"/>
-      <c r="I26" s="108"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110"/>
       <c r="J26" s="58">
         <v>3</v>
       </c>
-      <c r="K26" s="108">
+      <c r="K26" s="110">
         <v>4</v>
       </c>
-      <c r="L26" s="108"/>
-      <c r="M26" s="108"/>
-      <c r="N26" s="108">
+      <c r="L26" s="110"/>
+      <c r="M26" s="110"/>
+      <c r="N26" s="110">
         <v>5</v>
       </c>
-      <c r="O26" s="108"/>
-      <c r="P26" s="108"/>
-      <c r="Q26" s="108" t="s">
+      <c r="O26" s="110"/>
+      <c r="P26" s="110"/>
+      <c r="Q26" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="R26" s="108"/>
+      <c r="R26" s="110"/>
       <c r="S26" s="18"/>
     </row>
-    <row r="27" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="59"/>
-      <c r="B27" s="134"/>
-      <c r="C27" s="109"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="110"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="111"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="114"/>
+      <c r="E27" s="114"/>
+      <c r="F27" s="114"/>
+      <c r="G27" s="114"/>
+      <c r="H27" s="114"/>
+      <c r="I27" s="115"/>
       <c r="J27" s="60"/>
-      <c r="K27" s="135"/>
-      <c r="L27" s="136"/>
-      <c r="M27" s="137"/>
-      <c r="N27" s="138"/>
-      <c r="O27" s="139"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="140"/>
-      <c r="R27" s="141"/>
-      <c r="S27" s="30"/>
-    </row>
-    <row r="28" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K27" s="122"/>
+      <c r="L27" s="123"/>
+      <c r="M27" s="124"/>
+      <c r="N27" s="122"/>
+      <c r="O27" s="123"/>
+      <c r="P27" s="124"/>
+      <c r="Q27" s="116"/>
+      <c r="R27" s="117"/>
+      <c r="S27" s="27"/>
+    </row>
+    <row r="28" spans="1:19" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="59"/>
-      <c r="B28" s="62"/>
-      <c r="C28" s="63"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="62"/>
       <c r="D28" s="63"/>
       <c r="E28" s="63"/>
       <c r="F28" s="63"/>
       <c r="G28" s="63"/>
       <c r="H28" s="63"/>
       <c r="I28" s="63"/>
-      <c r="J28" s="113" t="s">
-        <v>42</v>
-      </c>
-      <c r="K28" s="113"/>
-      <c r="L28" s="113"/>
-      <c r="M28" s="113"/>
-      <c r="N28" s="113"/>
-      <c r="O28" s="113"/>
-      <c r="P28" s="114"/>
-      <c r="Q28" s="115"/>
-      <c r="R28" s="116"/>
-      <c r="S28" s="31"/>
-    </row>
-    <row r="29" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J28" s="118" t="s">
+        <v>41</v>
+      </c>
+      <c r="K28" s="118"/>
+      <c r="L28" s="118"/>
+      <c r="M28" s="118"/>
+      <c r="N28" s="118"/>
+      <c r="O28" s="118"/>
+      <c r="P28" s="119"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="121"/>
+      <c r="S28" s="28"/>
+    </row>
+    <row r="29" spans="1:19" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="59"/>
-      <c r="B29" s="118" t="s">
+      <c r="B29" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="119"/>
+      <c r="C29" s="127"/>
+      <c r="D29" s="127"/>
+      <c r="E29" s="127"/>
+      <c r="F29" s="127"/>
       <c r="G29" s="64"/>
       <c r="H29" s="65"/>
       <c r="I29" s="64"/>
-      <c r="J29" s="113" t="s">
-        <v>43</v>
-      </c>
-      <c r="K29" s="113"/>
-      <c r="L29" s="113"/>
-      <c r="M29" s="113"/>
-      <c r="N29" s="113"/>
-      <c r="O29" s="113"/>
-      <c r="P29" s="114"/>
-      <c r="Q29" s="115"/>
-      <c r="R29" s="116"/>
-      <c r="S29" s="31"/>
-    </row>
-    <row r="30" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J29" s="118" t="s">
+        <v>42</v>
+      </c>
+      <c r="K29" s="118"/>
+      <c r="L29" s="118"/>
+      <c r="M29" s="118"/>
+      <c r="N29" s="118"/>
+      <c r="O29" s="118"/>
+      <c r="P29" s="119"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="121"/>
+      <c r="S29" s="28"/>
+    </row>
+    <row r="30" spans="1:19" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="59"/>
       <c r="B30" s="66"/>
       <c r="C30" s="64"/>
@@ -3062,44 +3033,44 @@
       <c r="G30" s="64"/>
       <c r="H30" s="64"/>
       <c r="I30" s="64"/>
-      <c r="J30" s="113" t="s">
-        <v>44</v>
-      </c>
-      <c r="K30" s="113"/>
-      <c r="L30" s="113"/>
-      <c r="M30" s="113"/>
-      <c r="N30" s="113"/>
-      <c r="O30" s="113"/>
-      <c r="P30" s="114"/>
-      <c r="Q30" s="115"/>
-      <c r="R30" s="116"/>
-      <c r="S30" s="31"/>
-    </row>
-    <row r="31" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="55"/>
-      <c r="B31" s="131" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="132"/>
-      <c r="H31" s="132"/>
-      <c r="I31" s="132"/>
-      <c r="J31" s="132"/>
-      <c r="K31" s="132"/>
-      <c r="L31" s="132"/>
-      <c r="M31" s="132"/>
-      <c r="N31" s="132"/>
-      <c r="O31" s="132"/>
-      <c r="P31" s="132"/>
-      <c r="Q31" s="132"/>
-      <c r="R31" s="133"/>
+      <c r="J30" s="118" t="s">
+        <v>43</v>
+      </c>
+      <c r="K30" s="118"/>
+      <c r="L30" s="118"/>
+      <c r="M30" s="118"/>
+      <c r="N30" s="118"/>
+      <c r="O30" s="118"/>
+      <c r="P30" s="119"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="121"/>
+      <c r="S30" s="28"/>
+    </row>
+    <row r="31" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="52"/>
+      <c r="B31" s="91" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="128"/>
+      <c r="H31" s="128"/>
+      <c r="I31" s="128"/>
+      <c r="J31" s="128"/>
+      <c r="K31" s="128"/>
+      <c r="L31" s="128"/>
+      <c r="M31" s="128"/>
+      <c r="N31" s="128"/>
+      <c r="O31" s="128"/>
+      <c r="P31" s="128"/>
+      <c r="Q31" s="128"/>
+      <c r="R31" s="129"/>
       <c r="S31" s="19"/>
     </row>
-    <row r="32" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="37"/>
+    <row r="32" spans="1:19" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="34"/>
       <c r="B32" s="67"/>
       <c r="C32" s="68"/>
       <c r="D32" s="68"/>
@@ -3119,340 +3090,344 @@
       <c r="R32" s="70"/>
       <c r="S32" s="20"/>
     </row>
-    <row r="33" spans="1:19" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" s="7" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="71"/>
       <c r="B33" s="72"/>
-      <c r="C33" s="124" t="s">
+      <c r="C33" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="124"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="124"/>
-      <c r="G33" s="124"/>
-      <c r="H33" s="124"/>
-      <c r="I33" s="124"/>
-      <c r="J33" s="124"/>
-      <c r="K33" s="124"/>
-      <c r="L33" s="124" t="s">
-        <v>39</v>
-      </c>
-      <c r="M33" s="124"/>
-      <c r="N33" s="124"/>
-      <c r="O33" s="124"/>
-      <c r="P33" s="124"/>
-      <c r="Q33" s="124"/>
-      <c r="R33" s="124"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="137"/>
+      <c r="F33" s="137"/>
+      <c r="G33" s="137"/>
+      <c r="H33" s="137"/>
+      <c r="I33" s="137"/>
+      <c r="J33" s="137"/>
+      <c r="K33" s="137"/>
+      <c r="L33" s="137" t="s">
+        <v>38</v>
+      </c>
+      <c r="M33" s="137"/>
+      <c r="N33" s="137"/>
+      <c r="O33" s="137"/>
+      <c r="P33" s="137"/>
+      <c r="Q33" s="137"/>
+      <c r="R33" s="137"/>
       <c r="S33" s="21"/>
     </row>
-    <row r="34" spans="1:19" s="8" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" s="8" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="73"/>
       <c r="B34" s="74"/>
-      <c r="C34" s="117" t="s">
+      <c r="C34" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="117"/>
-      <c r="E34" s="117"/>
-      <c r="F34" s="117"/>
-      <c r="G34" s="117"/>
-      <c r="H34" s="117"/>
-      <c r="I34" s="117"/>
-      <c r="J34" s="117"/>
-      <c r="K34" s="117"/>
-      <c r="L34" s="117" t="s">
+      <c r="D34" s="125"/>
+      <c r="E34" s="125"/>
+      <c r="F34" s="125"/>
+      <c r="G34" s="125"/>
+      <c r="H34" s="125"/>
+      <c r="I34" s="125"/>
+      <c r="J34" s="125"/>
+      <c r="K34" s="125"/>
+      <c r="L34" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="M34" s="117"/>
-      <c r="N34" s="117"/>
-      <c r="O34" s="117"/>
-      <c r="P34" s="117"/>
-      <c r="Q34" s="117"/>
-      <c r="R34" s="117"/>
+      <c r="M34" s="125"/>
+      <c r="N34" s="125"/>
+      <c r="O34" s="125"/>
+      <c r="P34" s="125"/>
+      <c r="Q34" s="125"/>
+      <c r="R34" s="125"/>
       <c r="S34" s="22"/>
     </row>
-    <row r="35" spans="1:19" s="9" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="56"/>
+    <row r="35" spans="1:19" s="9" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="55"/>
       <c r="B35" s="75"/>
-      <c r="C35" s="112" t="s">
+      <c r="C35" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="112"/>
-      <c r="E35" s="112"/>
-      <c r="F35" s="112"/>
-      <c r="G35" s="112"/>
-      <c r="H35" s="112"/>
-      <c r="I35" s="112"/>
-      <c r="J35" s="112"/>
-      <c r="K35" s="112"/>
-      <c r="L35" s="112" t="s">
+      <c r="D35" s="138"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="138"/>
+      <c r="G35" s="138"/>
+      <c r="H35" s="138"/>
+      <c r="I35" s="138"/>
+      <c r="J35" s="138"/>
+      <c r="K35" s="138"/>
+      <c r="L35" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="M35" s="112"/>
-      <c r="N35" s="112"/>
-      <c r="O35" s="112"/>
-      <c r="P35" s="112"/>
-      <c r="Q35" s="112"/>
-      <c r="R35" s="112"/>
+      <c r="M35" s="138"/>
+      <c r="N35" s="138"/>
+      <c r="O35" s="138"/>
+      <c r="P35" s="138"/>
+      <c r="Q35" s="138"/>
+      <c r="R35" s="138"/>
       <c r="S35" s="23"/>
     </row>
-    <row r="36" spans="1:19" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="37"/>
-      <c r="B36" s="42"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="42"/>
-      <c r="R36" s="42"/>
+    <row r="36" spans="1:19" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="34"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
+      <c r="K36" s="39"/>
+      <c r="L36" s="39"/>
+      <c r="M36" s="39"/>
+      <c r="N36" s="39"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="39"/>
+      <c r="Q36" s="39"/>
+      <c r="R36" s="39"/>
       <c r="S36" s="24"/>
     </row>
-    <row r="37" spans="1:19" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="42"/>
-      <c r="K37" s="38"/>
-      <c r="L37" s="76" t="s">
+    <row r="37" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="34"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="M37" s="77"/>
-      <c r="N37" s="77"/>
-      <c r="O37" s="77"/>
-      <c r="P37" s="78"/>
-      <c r="Q37" s="78"/>
-      <c r="R37" s="79"/>
-      <c r="S37" s="25"/>
-    </row>
-    <row r="38" spans="1:19" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A38" s="80"/>
-      <c r="B38" s="81"/>
-      <c r="C38" s="81"/>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="82"/>
-      <c r="G38" s="82"/>
-      <c r="H38" s="82"/>
-      <c r="I38" s="82"/>
-      <c r="J38" s="82"/>
-      <c r="K38" s="81"/>
-      <c r="L38" s="127" t="s">
-        <v>45</v>
-      </c>
-      <c r="M38" s="128"/>
-      <c r="N38" s="128"/>
-      <c r="O38" s="128"/>
-      <c r="P38" s="128"/>
-      <c r="Q38" s="128"/>
-      <c r="R38" s="129"/>
-      <c r="S38" s="26"/>
-    </row>
-    <row r="39" spans="1:19" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="37"/>
-      <c r="B39" s="83"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="42"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="130" t="s">
+      <c r="M37" s="76"/>
+      <c r="N37" s="76"/>
+      <c r="O37" s="130"/>
+      <c r="P37" s="130"/>
+      <c r="Q37" s="130"/>
+      <c r="R37" s="131"/>
+      <c r="S37" s="142"/>
+    </row>
+    <row r="38" spans="1:19" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A38" s="77"/>
+      <c r="B38" s="78"/>
+      <c r="C38" s="78"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="78"/>
+      <c r="F38" s="79"/>
+      <c r="G38" s="79"/>
+      <c r="H38" s="79"/>
+      <c r="I38" s="79"/>
+      <c r="J38" s="79"/>
+      <c r="K38" s="78"/>
+      <c r="L38" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="M38" s="98"/>
+      <c r="N38" s="98"/>
+      <c r="O38" s="95"/>
+      <c r="P38" s="95"/>
+      <c r="Q38" s="95"/>
+      <c r="R38" s="96"/>
+      <c r="S38" s="143"/>
+    </row>
+    <row r="39" spans="1:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="34"/>
+      <c r="B39" s="80"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
+      <c r="H39" s="39"/>
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="35"/>
+      <c r="L39" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="M39" s="84"/>
-      <c r="N39" s="85"/>
-      <c r="O39" s="85"/>
-      <c r="P39" s="85"/>
-      <c r="Q39" s="85"/>
-      <c r="R39" s="86"/>
-      <c r="S39" s="27"/>
-    </row>
-    <row r="40" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="37"/>
-      <c r="B40" s="87"/>
-      <c r="C40" s="88"/>
-      <c r="D40" s="88"/>
-      <c r="E40" s="88"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
-      <c r="K40" s="42"/>
-      <c r="L40" s="42"/>
-      <c r="M40" s="42"/>
-      <c r="N40" s="42"/>
-      <c r="O40" s="42"/>
-      <c r="P40" s="42"/>
-      <c r="Q40" s="42"/>
-      <c r="R40" s="42"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="83"/>
+      <c r="O39" s="132"/>
+      <c r="P39" s="132"/>
+      <c r="Q39" s="132"/>
+      <c r="R39" s="133"/>
+      <c r="S39" s="144"/>
+    </row>
+    <row r="40" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="34"/>
+      <c r="B40" s="84"/>
+      <c r="C40" s="85"/>
+      <c r="D40" s="85"/>
+      <c r="E40" s="85"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39"/>
+      <c r="K40" s="39"/>
+      <c r="L40" s="39"/>
+      <c r="M40" s="39"/>
+      <c r="N40" s="39"/>
+      <c r="O40" s="39"/>
+      <c r="P40" s="39"/>
+      <c r="Q40" s="39"/>
+      <c r="R40" s="39"/>
       <c r="S40" s="24"/>
     </row>
-    <row r="41" spans="1:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
-      <c r="B41" s="89" t="s">
+    <row r="41" spans="1:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="34"/>
+      <c r="B41" s="86" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="87"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="87"/>
+      <c r="F41" s="87"/>
+      <c r="G41" s="140"/>
+      <c r="H41" s="140"/>
+      <c r="I41" s="140"/>
+      <c r="J41" s="140"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="84"/>
+      <c r="M41" s="39"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="39"/>
+      <c r="P41" s="39"/>
+      <c r="Q41" s="39"/>
+      <c r="R41" s="39"/>
+      <c r="S41" s="24"/>
+    </row>
+    <row r="42" spans="1:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="34"/>
+      <c r="B42" s="139" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="126"/>
-      <c r="H41" s="126"/>
-      <c r="I41" s="126"/>
-      <c r="J41" s="126"/>
-      <c r="K41" s="38"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="42"/>
-      <c r="N41" s="42"/>
-      <c r="O41" s="42"/>
-      <c r="P41" s="42"/>
-      <c r="Q41" s="42"/>
-      <c r="R41" s="42"/>
-      <c r="S41" s="24"/>
-    </row>
-    <row r="42" spans="1:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="37"/>
-      <c r="B42" s="125" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42" s="125"/>
-      <c r="D42" s="125"/>
-      <c r="E42" s="125"/>
-      <c r="F42" s="125"/>
-      <c r="G42" s="125"/>
-      <c r="H42" s="125"/>
-      <c r="I42" s="125"/>
-      <c r="J42" s="125"/>
-      <c r="K42" s="125"/>
-      <c r="L42" s="87"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="42"/>
-      <c r="R42" s="42"/>
+      <c r="C42" s="139"/>
+      <c r="D42" s="139"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="139"/>
+      <c r="H42" s="139"/>
+      <c r="I42" s="139"/>
+      <c r="J42" s="139"/>
+      <c r="K42" s="139"/>
+      <c r="L42" s="84"/>
+      <c r="M42" s="39"/>
+      <c r="N42" s="39"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="39"/>
+      <c r="Q42" s="39"/>
+      <c r="R42" s="39"/>
       <c r="S42" s="24"/>
     </row>
-    <row r="43" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="91"/>
-      <c r="B43" s="122" t="s">
+    <row r="43" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="88"/>
+      <c r="B43" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="122"/>
-      <c r="D43" s="122"/>
-      <c r="E43" s="122"/>
-      <c r="F43" s="122"/>
-      <c r="G43" s="122"/>
-      <c r="H43" s="122"/>
-      <c r="I43" s="122"/>
-      <c r="J43" s="122"/>
-      <c r="K43" s="122"/>
-      <c r="L43" s="122"/>
-      <c r="M43" s="122"/>
-      <c r="N43" s="122"/>
-      <c r="O43" s="122"/>
-      <c r="P43" s="122"/>
-      <c r="Q43" s="122"/>
-      <c r="R43" s="122"/>
-      <c r="S43" s="28"/>
-    </row>
-    <row r="44" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="38"/>
-      <c r="B44" s="123" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" s="123"/>
-      <c r="D44" s="123"/>
-      <c r="E44" s="123"/>
-      <c r="F44" s="123"/>
-      <c r="G44" s="123"/>
-      <c r="H44" s="123"/>
-      <c r="I44" s="123"/>
-      <c r="J44" s="123"/>
-      <c r="K44" s="123"/>
-      <c r="L44" s="123"/>
-      <c r="M44" s="123"/>
-      <c r="N44" s="123"/>
-      <c r="O44" s="123"/>
-      <c r="P44" s="123"/>
-      <c r="Q44" s="123"/>
-      <c r="R44" s="123"/>
+      <c r="C43" s="135"/>
+      <c r="D43" s="135"/>
+      <c r="E43" s="135"/>
+      <c r="F43" s="135"/>
+      <c r="G43" s="135"/>
+      <c r="H43" s="135"/>
+      <c r="I43" s="135"/>
+      <c r="J43" s="135"/>
+      <c r="K43" s="135"/>
+      <c r="L43" s="135"/>
+      <c r="M43" s="135"/>
+      <c r="N43" s="135"/>
+      <c r="O43" s="135"/>
+      <c r="P43" s="135"/>
+      <c r="Q43" s="135"/>
+      <c r="R43" s="135"/>
+      <c r="S43" s="25"/>
+    </row>
+    <row r="44" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="35"/>
+      <c r="B44" s="136" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="136"/>
+      <c r="D44" s="136"/>
+      <c r="E44" s="136"/>
+      <c r="F44" s="136"/>
+      <c r="G44" s="136"/>
+      <c r="H44" s="136"/>
+      <c r="I44" s="136"/>
+      <c r="J44" s="136"/>
+      <c r="K44" s="136"/>
+      <c r="L44" s="136"/>
+      <c r="M44" s="136"/>
+      <c r="N44" s="136"/>
+      <c r="O44" s="136"/>
+      <c r="P44" s="136"/>
+      <c r="Q44" s="136"/>
+      <c r="R44" s="136"/>
       <c r="S44" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="54">
-    <mergeCell ref="I14:R14"/>
+  <mergeCells count="58">
+    <mergeCell ref="F5:N5"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="O39:R39"/>
     <mergeCell ref="F4:M4"/>
     <mergeCell ref="B43:R43"/>
     <mergeCell ref="B44:R44"/>
     <mergeCell ref="L33:R33"/>
     <mergeCell ref="L34:R34"/>
     <mergeCell ref="L35:R35"/>
-    <mergeCell ref="L38:R38"/>
     <mergeCell ref="B42:K42"/>
     <mergeCell ref="G41:J41"/>
     <mergeCell ref="Q30:R30"/>
     <mergeCell ref="H33:K33"/>
     <mergeCell ref="C33:G33"/>
     <mergeCell ref="H34:K34"/>
-    <mergeCell ref="G31:R31"/>
     <mergeCell ref="H35:K35"/>
     <mergeCell ref="C35:G35"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:R28"/>
     <mergeCell ref="C34:G34"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="J29:P29"/>
     <mergeCell ref="Q29:R29"/>
     <mergeCell ref="J30:P30"/>
+    <mergeCell ref="G31:R31"/>
     <mergeCell ref="C27:I27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="N27:O27"/>
     <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="K24:M24"/>
     <mergeCell ref="N24:P24"/>
     <mergeCell ref="C25:I25"/>
     <mergeCell ref="K25:M25"/>
     <mergeCell ref="N25:P25"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="E19:R19"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="L38:N38"/>
     <mergeCell ref="F11:R11"/>
     <mergeCell ref="N2:Q2"/>
     <mergeCell ref="N3:Q3"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="G7:O7"/>
-    <mergeCell ref="F5:L5"/>
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="F3:M3"/>
     <mergeCell ref="F9:R9"/>
     <mergeCell ref="F10:R10"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q26:R26"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_111_VAT INVOICE_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_111_VAT INVOICE_IMP.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAP-DEV-030\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\GENUWIN\19. Package\98. 2205 WABOOK\1.2307 WeTAX\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="4" r:id="rId1"/>
@@ -333,6 +333,71 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>Ngày /</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Date</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> tháng / </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>month</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">    năm /</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>year</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+  </si>
+  <si>
     <t>VAT INVOICE</t>
   </si>
   <si>
@@ -604,62 +669,6 @@
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">: </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ngày /</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Date   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> tháng / </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>month</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">    năm /</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>year</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
     </r>
   </si>
 </sst>
@@ -667,7 +676,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="55" x14ac:knownFonts="1">
+  <fonts count="54" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -698,12 +707,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1514,50 +1517,50 @@
   </borders>
   <cellStyleXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyFont="0" applyFill="0"/>
     <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyFont="0" applyFill="0"/>
     <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyFont="0" applyFill="0"/>
     <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyFont="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="2" applyFont="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="2" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyFont="0" applyFill="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyFont="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyFont="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyFont="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyFont="0"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyFont="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyFont="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyFont="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyFont="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1566,10 +1569,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1578,94 +1581,101 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="30" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="30" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1674,20 +1684,20 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1696,16 +1706,16 @@
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1717,52 +1727,49 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1771,35 +1778,38 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1808,176 +1818,163 @@
     <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="51" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="26" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2302,1075 +2299,1116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S44"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="1.7109375" style="1" customWidth="1"/>
-    <col min="6" max="7" width="5.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="1.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="0.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.7109375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="4.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="0.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="1.7109375" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.28515625" style="1"/>
+    <col min="1" max="1" width="1.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="1.6640625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="5.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="1.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="4.33203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="0.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="5.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="4.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="0.6640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="1.6640625" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29"/>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-    </row>
-    <row r="2" spans="1:19" ht="25.15" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="103" t="s">
+    <row r="1" spans="1:19" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+    </row>
+    <row r="2" spans="1:19" ht="25.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="100" t="s">
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="124" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="124"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="11"/>
+    </row>
+    <row r="3" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="130" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="125" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="12"/>
+    </row>
+    <row r="4" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="37"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="12"/>
+    </row>
+    <row r="5" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="37"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="128" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="13"/>
+    </row>
+    <row r="6" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="37"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="13"/>
+    </row>
+    <row r="7" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="37"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="126" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="127"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="127"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="127"/>
+      <c r="O7" s="127"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="13"/>
+    </row>
+    <row r="8" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="12"/>
+    </row>
+    <row r="9" spans="1:19" ht="25.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="43"/>
+      <c r="B9" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="132"/>
+      <c r="G9" s="132"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="132"/>
+      <c r="J9" s="132"/>
+      <c r="K9" s="132"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="132"/>
+      <c r="N9" s="132"/>
+      <c r="O9" s="132"/>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="132"/>
+      <c r="R9" s="132"/>
+      <c r="S9" s="14"/>
+    </row>
+    <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="37"/>
+      <c r="B10" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="131"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="131"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
+      <c r="R10" s="131"/>
+      <c r="S10" s="12"/>
+    </row>
+    <row r="11" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="37"/>
+      <c r="B11" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="119"/>
+      <c r="K11" s="119"/>
+      <c r="L11" s="119"/>
+      <c r="M11" s="119"/>
+      <c r="N11" s="119"/>
+      <c r="O11" s="119"/>
+      <c r="P11" s="119"/>
+      <c r="Q11" s="119"/>
+      <c r="R11" s="119"/>
+      <c r="S11" s="12"/>
+    </row>
+    <row r="12" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="37"/>
+      <c r="B12" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="115"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="115"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="115"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="13"/>
+    </row>
+    <row r="13" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="37"/>
+      <c r="B13" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="115"/>
+      <c r="K13" s="115"/>
+      <c r="L13" s="115"/>
+      <c r="M13" s="115"/>
+      <c r="N13" s="115"/>
+      <c r="O13" s="115"/>
+      <c r="P13" s="115"/>
+      <c r="Q13" s="115"/>
+      <c r="R13" s="115"/>
+      <c r="S13" s="13"/>
+    </row>
+    <row r="14" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="37"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="116"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="116"/>
+      <c r="K14" s="116"/>
+      <c r="L14" s="116"/>
+      <c r="M14" s="116"/>
+      <c r="N14" s="116"/>
+      <c r="O14" s="116"/>
+      <c r="P14" s="116"/>
+      <c r="Q14" s="116"/>
+      <c r="R14" s="116"/>
+      <c r="S14" s="13"/>
+    </row>
+    <row r="15" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="37"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="13"/>
+    </row>
+    <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="37"/>
+      <c r="B16" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="51"/>
+      <c r="M16" s="51"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="51"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="51"/>
+      <c r="R16" s="51"/>
+      <c r="S16" s="29"/>
+    </row>
+    <row r="17" spans="1:19" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="37"/>
+      <c r="B17" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
+      <c r="P17" s="52"/>
+      <c r="Q17" s="52"/>
+      <c r="R17" s="52"/>
+      <c r="S17" s="15"/>
+    </row>
+    <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="37"/>
+      <c r="B18" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="53"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="53"/>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="53"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="15"/>
+    </row>
+    <row r="19" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="37"/>
+      <c r="B19" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="119"/>
+      <c r="O19" s="119"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="119"/>
+      <c r="R19" s="119"/>
+      <c r="S19" s="15"/>
+    </row>
+    <row r="20" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="37"/>
+      <c r="B20" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="15"/>
+    </row>
+    <row r="21" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="37"/>
+      <c r="B21" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="12"/>
+    </row>
+    <row r="22" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="37"/>
+      <c r="B22" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="12"/>
+    </row>
+    <row r="23" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="37"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="12"/>
+    </row>
+    <row r="24" spans="1:19" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A24" s="55"/>
+      <c r="B24" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="117" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="117"/>
+      <c r="J24" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" s="117" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="117"/>
+      <c r="M24" s="117"/>
+      <c r="N24" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="117"/>
+      <c r="P24" s="117"/>
+      <c r="Q24" s="117" t="s">
+        <v>7</v>
+      </c>
+      <c r="R24" s="117"/>
+      <c r="S24" s="16"/>
+    </row>
+    <row r="25" spans="1:19" s="4" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="58"/>
+      <c r="B25" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="118"/>
+      <c r="H25" s="118"/>
+      <c r="I25" s="118"/>
+      <c r="J25" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" s="118" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25" s="118"/>
+      <c r="M25" s="118"/>
+      <c r="N25" s="118" t="s">
+        <v>6</v>
+      </c>
+      <c r="O25" s="118"/>
+      <c r="P25" s="118"/>
+      <c r="Q25" s="118" t="s">
+        <v>8</v>
+      </c>
+      <c r="R25" s="118"/>
+      <c r="S25" s="17"/>
+    </row>
+    <row r="26" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="60"/>
+      <c r="B26" s="61">
+        <v>1</v>
+      </c>
+      <c r="C26" s="114">
+        <v>2</v>
+      </c>
+      <c r="D26" s="114"/>
+      <c r="E26" s="114"/>
+      <c r="F26" s="114"/>
+      <c r="G26" s="114"/>
+      <c r="H26" s="114"/>
+      <c r="I26" s="114"/>
+      <c r="J26" s="61">
+        <v>3</v>
+      </c>
+      <c r="K26" s="114">
+        <v>4</v>
+      </c>
+      <c r="L26" s="114"/>
+      <c r="M26" s="114"/>
+      <c r="N26" s="114">
+        <v>5</v>
+      </c>
+      <c r="O26" s="114"/>
+      <c r="P26" s="114"/>
+      <c r="Q26" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="R26" s="114"/>
+      <c r="S26" s="18"/>
+    </row>
+    <row r="27" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="62"/>
+      <c r="B27" s="133"/>
+      <c r="C27" s="134"/>
+      <c r="D27" s="135"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="135"/>
+      <c r="G27" s="135"/>
+      <c r="H27" s="135"/>
+      <c r="I27" s="136"/>
+      <c r="J27" s="137"/>
+      <c r="K27" s="138"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="140"/>
+      <c r="N27" s="138"/>
+      <c r="O27" s="139"/>
+      <c r="P27" s="140"/>
+      <c r="Q27" s="141"/>
+      <c r="R27" s="142"/>
+      <c r="S27" s="30"/>
+    </row>
+    <row r="28" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="62"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="65"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="110" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" s="110"/>
+      <c r="L28" s="110"/>
+      <c r="M28" s="110"/>
+      <c r="N28" s="110"/>
+      <c r="O28" s="110"/>
+      <c r="P28" s="111"/>
+      <c r="Q28" s="106"/>
+      <c r="R28" s="107"/>
+      <c r="S28" s="31"/>
+    </row>
+    <row r="29" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="62"/>
+      <c r="B29" s="108" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="109"/>
+      <c r="D29" s="109"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="110" t="s">
+        <v>43</v>
+      </c>
+      <c r="K29" s="110"/>
+      <c r="L29" s="110"/>
+      <c r="M29" s="110"/>
+      <c r="N29" s="110"/>
+      <c r="O29" s="110"/>
+      <c r="P29" s="111"/>
+      <c r="Q29" s="106"/>
+      <c r="R29" s="107"/>
+      <c r="S29" s="31"/>
+    </row>
+    <row r="30" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="62"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="110" t="s">
+        <v>44</v>
+      </c>
+      <c r="K30" s="110"/>
+      <c r="L30" s="110"/>
+      <c r="M30" s="110"/>
+      <c r="N30" s="110"/>
+      <c r="O30" s="110"/>
+      <c r="P30" s="111"/>
+      <c r="Q30" s="106"/>
+      <c r="R30" s="107"/>
+      <c r="S30" s="31"/>
+    </row>
+    <row r="31" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="55"/>
+      <c r="B31" s="92" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="112"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="112"/>
+      <c r="K31" s="112"/>
+      <c r="L31" s="112"/>
+      <c r="M31" s="112"/>
+      <c r="N31" s="112"/>
+      <c r="O31" s="112"/>
+      <c r="P31" s="112"/>
+      <c r="Q31" s="112"/>
+      <c r="R31" s="113"/>
+      <c r="S31" s="19"/>
+    </row>
+    <row r="32" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="37"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="71"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="71"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="20"/>
+    </row>
+    <row r="33" spans="1:19" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="73"/>
+      <c r="B33" s="74"/>
+      <c r="C33" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="101"/>
+      <c r="E33" s="101"/>
+      <c r="F33" s="101"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="101"/>
+      <c r="I33" s="101"/>
+      <c r="J33" s="101"/>
+      <c r="K33" s="101"/>
+      <c r="L33" s="101" t="s">
+        <v>39</v>
+      </c>
+      <c r="M33" s="101"/>
+      <c r="N33" s="101"/>
+      <c r="O33" s="101"/>
+      <c r="P33" s="101"/>
+      <c r="Q33" s="101"/>
+      <c r="R33" s="101"/>
+      <c r="S33" s="21"/>
+    </row>
+    <row r="34" spans="1:19" s="8" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="75"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="102" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="102"/>
+      <c r="E34" s="102"/>
+      <c r="F34" s="102"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="102"/>
+      <c r="I34" s="102"/>
+      <c r="J34" s="102"/>
+      <c r="K34" s="102"/>
+      <c r="L34" s="102" t="s">
+        <v>9</v>
+      </c>
+      <c r="M34" s="102"/>
+      <c r="N34" s="102"/>
+      <c r="O34" s="102"/>
+      <c r="P34" s="102"/>
+      <c r="Q34" s="102"/>
+      <c r="R34" s="102"/>
+      <c r="S34" s="22"/>
+    </row>
+    <row r="35" spans="1:19" s="9" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="58"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="103" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="103"/>
+      <c r="J35" s="103"/>
+      <c r="K35" s="103"/>
+      <c r="L35" s="103" t="s">
+        <v>10</v>
+      </c>
+      <c r="M35" s="103"/>
+      <c r="N35" s="103"/>
+      <c r="O35" s="103"/>
+      <c r="P35" s="103"/>
+      <c r="Q35" s="103"/>
+      <c r="R35" s="103"/>
+      <c r="S35" s="23"/>
+    </row>
+    <row r="36" spans="1:19" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="37"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="42"/>
+      <c r="R36" s="42"/>
+      <c r="S36" s="24"/>
+    </row>
+    <row r="37" spans="1:19" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="37"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="91" t="s">
+        <v>12</v>
+      </c>
+      <c r="M37" s="78"/>
+      <c r="N37" s="78"/>
+      <c r="O37" s="94"/>
+      <c r="P37" s="94"/>
+      <c r="Q37" s="94"/>
+      <c r="R37" s="95"/>
+      <c r="S37" s="25"/>
+    </row>
+    <row r="38" spans="1:19" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A38" s="79"/>
+      <c r="B38" s="80"/>
+      <c r="C38" s="80"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="81"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="100"/>
-      <c r="P2" s="100"/>
-      <c r="Q2" s="100"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="11"/>
-    </row>
-    <row r="3" spans="1:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="104" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="101" t="s">
-        <v>46</v>
-      </c>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="12"/>
-    </row>
-    <row r="4" spans="1:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="134"/>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
-      <c r="M4" s="134"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="12"/>
-    </row>
-    <row r="5" spans="1:19" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="141" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" s="141"/>
-      <c r="H5" s="141"/>
-      <c r="I5" s="141"/>
-      <c r="J5" s="141"/>
-      <c r="K5" s="141"/>
-      <c r="L5" s="141"/>
-      <c r="M5" s="141"/>
-      <c r="N5" s="141"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="13"/>
-    </row>
-    <row r="6" spans="1:19" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="34"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="13"/>
-    </row>
-    <row r="7" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="34"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="101" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="13"/>
-    </row>
-    <row r="8" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="34"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="12"/>
-    </row>
-    <row r="9" spans="1:19" ht="25.15" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="40"/>
-      <c r="B9" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="105"/>
-      <c r="L9" s="105"/>
-      <c r="M9" s="105"/>
-      <c r="N9" s="105"/>
-      <c r="O9" s="105"/>
-      <c r="P9" s="105"/>
-      <c r="Q9" s="105"/>
-      <c r="R9" s="105"/>
-      <c r="S9" s="14"/>
-    </row>
-    <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="34"/>
-      <c r="B10" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="106"/>
-      <c r="N10" s="106"/>
-      <c r="O10" s="106"/>
-      <c r="P10" s="106"/>
-      <c r="Q10" s="106"/>
-      <c r="R10" s="106"/>
-      <c r="S10" s="12"/>
-    </row>
-    <row r="11" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="34"/>
-      <c r="B11" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="99"/>
-      <c r="G11" s="99"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="99"/>
-      <c r="K11" s="99"/>
-      <c r="L11" s="99"/>
-      <c r="M11" s="99"/>
-      <c r="N11" s="99"/>
-      <c r="O11" s="99"/>
-      <c r="P11" s="99"/>
-      <c r="Q11" s="99"/>
-      <c r="R11" s="99"/>
-      <c r="S11" s="12"/>
-    </row>
-    <row r="12" spans="1:19" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34"/>
-      <c r="B12" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="107"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="107"/>
-      <c r="I12" s="107"/>
-      <c r="J12" s="107"/>
-      <c r="K12" s="93"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="93"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="94"/>
-      <c r="P12" s="93"/>
-      <c r="Q12" s="93"/>
-      <c r="R12" s="93"/>
-      <c r="S12" s="13"/>
-    </row>
-    <row r="13" spans="1:19" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="B13" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="107"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="107"/>
-      <c r="K13" s="107"/>
-      <c r="L13" s="107"/>
-      <c r="M13" s="107"/>
-      <c r="N13" s="107"/>
-      <c r="O13" s="107"/>
-      <c r="P13" s="107"/>
-      <c r="Q13" s="107"/>
-      <c r="R13" s="107"/>
-      <c r="S13" s="13"/>
-    </row>
-    <row r="14" spans="1:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="34"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="111"/>
-      <c r="L14" s="111"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="111"/>
-      <c r="P14" s="111"/>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="111"/>
-      <c r="S14" s="13"/>
-    </row>
-    <row r="15" spans="1:19" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="34"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
-      <c r="O15" s="46"/>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="46"/>
-      <c r="S15" s="13"/>
-    </row>
-    <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="34"/>
-      <c r="B16" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="48"/>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="48"/>
-      <c r="R16" s="48"/>
-      <c r="S16" s="26"/>
-    </row>
-    <row r="17" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="34"/>
-      <c r="B17" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="49"/>
-      <c r="N17" s="49"/>
-      <c r="O17" s="49"/>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="49"/>
-      <c r="R17" s="49"/>
-      <c r="S17" s="15"/>
-    </row>
-    <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="34"/>
-      <c r="B18" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="50"/>
-      <c r="P18" s="50"/>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="50"/>
-      <c r="S18" s="15"/>
-    </row>
-    <row r="19" spans="1:19" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="34"/>
-      <c r="B19" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="92"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="15"/>
-    </row>
-    <row r="20" spans="1:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="34"/>
-      <c r="B20" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="50"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="50"/>
-      <c r="S20" s="15"/>
-    </row>
-    <row r="21" spans="1:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="34"/>
-      <c r="B21" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="12"/>
-    </row>
-    <row r="22" spans="1:19" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="34"/>
-      <c r="B22" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="L22" s="35"/>
-      <c r="M22" s="35"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="12"/>
-    </row>
-    <row r="23" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="34"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="35"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="12"/>
-    </row>
-    <row r="24" spans="1:19" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="52"/>
-      <c r="B24" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="108" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="108"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="108"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="108"/>
-      <c r="I24" s="108"/>
-      <c r="J24" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="K24" s="108" t="s">
-        <v>4</v>
-      </c>
-      <c r="L24" s="108"/>
-      <c r="M24" s="108"/>
-      <c r="N24" s="108" t="s">
-        <v>5</v>
-      </c>
-      <c r="O24" s="108"/>
-      <c r="P24" s="108"/>
-      <c r="Q24" s="108" t="s">
-        <v>7</v>
-      </c>
-      <c r="R24" s="108"/>
-      <c r="S24" s="16"/>
-    </row>
-    <row r="25" spans="1:19" s="4" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="55"/>
-      <c r="B25" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C25" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="109"/>
-      <c r="E25" s="109"/>
-      <c r="F25" s="109"/>
-      <c r="G25" s="109"/>
-      <c r="H25" s="109"/>
-      <c r="I25" s="109"/>
-      <c r="J25" s="56" t="s">
-        <v>3</v>
-      </c>
-      <c r="K25" s="109" t="s">
-        <v>14</v>
-      </c>
-      <c r="L25" s="109"/>
-      <c r="M25" s="109"/>
-      <c r="N25" s="109" t="s">
-        <v>6</v>
-      </c>
-      <c r="O25" s="109"/>
-      <c r="P25" s="109"/>
-      <c r="Q25" s="109" t="s">
-        <v>8</v>
-      </c>
-      <c r="R25" s="109"/>
-      <c r="S25" s="17"/>
-    </row>
-    <row r="26" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="57"/>
-      <c r="B26" s="58">
-        <v>1</v>
-      </c>
-      <c r="C26" s="110">
-        <v>2</v>
-      </c>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="58">
-        <v>3</v>
-      </c>
-      <c r="K26" s="110">
-        <v>4</v>
-      </c>
-      <c r="L26" s="110"/>
-      <c r="M26" s="110"/>
-      <c r="N26" s="110">
-        <v>5</v>
-      </c>
-      <c r="O26" s="110"/>
-      <c r="P26" s="110"/>
-      <c r="Q26" s="110" t="s">
-        <v>18</v>
-      </c>
-      <c r="R26" s="110"/>
-      <c r="S26" s="18"/>
-    </row>
-    <row r="27" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="59"/>
-      <c r="B27" s="90"/>
-      <c r="C27" s="113"/>
-      <c r="D27" s="114"/>
-      <c r="E27" s="114"/>
-      <c r="F27" s="114"/>
-      <c r="G27" s="114"/>
-      <c r="H27" s="114"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="122"/>
-      <c r="L27" s="123"/>
-      <c r="M27" s="124"/>
-      <c r="N27" s="122"/>
-      <c r="O27" s="123"/>
-      <c r="P27" s="124"/>
-      <c r="Q27" s="116"/>
-      <c r="R27" s="117"/>
-      <c r="S27" s="27"/>
-    </row>
-    <row r="28" spans="1:19" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="59"/>
-      <c r="B28" s="61"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="118" t="s">
-        <v>41</v>
-      </c>
-      <c r="K28" s="118"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="118"/>
-      <c r="N28" s="118"/>
-      <c r="O28" s="118"/>
-      <c r="P28" s="119"/>
-      <c r="Q28" s="120"/>
-      <c r="R28" s="121"/>
-      <c r="S28" s="28"/>
-    </row>
-    <row r="29" spans="1:19" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="59"/>
-      <c r="B29" s="126" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="127"/>
-      <c r="D29" s="127"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="127"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="64"/>
-      <c r="J29" s="118" t="s">
-        <v>42</v>
-      </c>
-      <c r="K29" s="118"/>
-      <c r="L29" s="118"/>
-      <c r="M29" s="118"/>
-      <c r="N29" s="118"/>
-      <c r="O29" s="118"/>
-      <c r="P29" s="119"/>
-      <c r="Q29" s="120"/>
-      <c r="R29" s="121"/>
-      <c r="S29" s="28"/>
-    </row>
-    <row r="30" spans="1:19" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="59"/>
-      <c r="B30" s="66"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="118" t="s">
-        <v>43</v>
-      </c>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="118"/>
-      <c r="O30" s="118"/>
-      <c r="P30" s="119"/>
-      <c r="Q30" s="120"/>
-      <c r="R30" s="121"/>
-      <c r="S30" s="28"/>
-    </row>
-    <row r="31" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="52"/>
-      <c r="B31" s="91" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="128"/>
-      <c r="H31" s="128"/>
-      <c r="I31" s="128"/>
-      <c r="J31" s="128"/>
-      <c r="K31" s="128"/>
-      <c r="L31" s="128"/>
-      <c r="M31" s="128"/>
-      <c r="N31" s="128"/>
-      <c r="O31" s="128"/>
-      <c r="P31" s="128"/>
-      <c r="Q31" s="128"/>
-      <c r="R31" s="129"/>
-      <c r="S31" s="19"/>
-    </row>
-    <row r="32" spans="1:19" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="34"/>
-      <c r="B32" s="67"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="69"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="69"/>
-      <c r="I32" s="69"/>
-      <c r="J32" s="69"/>
-      <c r="K32" s="69"/>
-      <c r="L32" s="69"/>
-      <c r="M32" s="69"/>
-      <c r="N32" s="69"/>
-      <c r="O32" s="69"/>
-      <c r="P32" s="69"/>
-      <c r="Q32" s="69"/>
-      <c r="R32" s="70"/>
-      <c r="S32" s="20"/>
-    </row>
-    <row r="33" spans="1:19" s="7" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="71"/>
-      <c r="B33" s="72"/>
-      <c r="C33" s="137" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="137"/>
-      <c r="E33" s="137"/>
-      <c r="F33" s="137"/>
-      <c r="G33" s="137"/>
-      <c r="H33" s="137"/>
-      <c r="I33" s="137"/>
-      <c r="J33" s="137"/>
-      <c r="K33" s="137"/>
-      <c r="L33" s="137" t="s">
+      <c r="M38" s="123"/>
+      <c r="N38" s="123"/>
+      <c r="O38" s="120"/>
+      <c r="P38" s="120"/>
+      <c r="Q38" s="120"/>
+      <c r="R38" s="121"/>
+      <c r="S38" s="26"/>
+    </row>
+    <row r="39" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="37"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="83" t="s">
+        <v>15</v>
+      </c>
+      <c r="M39" s="84"/>
+      <c r="N39" s="85"/>
+      <c r="O39" s="96"/>
+      <c r="P39" s="96"/>
+      <c r="Q39" s="96"/>
+      <c r="R39" s="97"/>
+      <c r="S39" s="27"/>
+    </row>
+    <row r="40" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="37"/>
+      <c r="B40" s="86"/>
+      <c r="C40" s="87"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="42"/>
+      <c r="L40" s="42"/>
+      <c r="M40" s="42"/>
+      <c r="N40" s="42"/>
+      <c r="O40" s="42"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="42"/>
+      <c r="R40" s="42"/>
+      <c r="S40" s="24"/>
+    </row>
+    <row r="41" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="37"/>
+      <c r="B41" s="88" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="89"/>
+      <c r="D41" s="89"/>
+      <c r="E41" s="89"/>
+      <c r="F41" s="89"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="105"/>
+      <c r="K41" s="38"/>
+      <c r="L41" s="86"/>
+      <c r="M41" s="42"/>
+      <c r="N41" s="42"/>
+      <c r="O41" s="42"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="42"/>
+      <c r="S41" s="24"/>
+    </row>
+    <row r="42" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="37"/>
+      <c r="B42" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="M33" s="137"/>
-      <c r="N33" s="137"/>
-      <c r="O33" s="137"/>
-      <c r="P33" s="137"/>
-      <c r="Q33" s="137"/>
-      <c r="R33" s="137"/>
-      <c r="S33" s="21"/>
-    </row>
-    <row r="34" spans="1:19" s="8" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="73"/>
-      <c r="B34" s="74"/>
-      <c r="C34" s="125" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="125"/>
-      <c r="E34" s="125"/>
-      <c r="F34" s="125"/>
-      <c r="G34" s="125"/>
-      <c r="H34" s="125"/>
-      <c r="I34" s="125"/>
-      <c r="J34" s="125"/>
-      <c r="K34" s="125"/>
-      <c r="L34" s="125" t="s">
-        <v>9</v>
-      </c>
-      <c r="M34" s="125"/>
-      <c r="N34" s="125"/>
-      <c r="O34" s="125"/>
-      <c r="P34" s="125"/>
-      <c r="Q34" s="125"/>
-      <c r="R34" s="125"/>
-      <c r="S34" s="22"/>
-    </row>
-    <row r="35" spans="1:19" s="9" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="55"/>
-      <c r="B35" s="75"/>
-      <c r="C35" s="138" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="138"/>
-      <c r="E35" s="138"/>
-      <c r="F35" s="138"/>
-      <c r="G35" s="138"/>
-      <c r="H35" s="138"/>
-      <c r="I35" s="138"/>
-      <c r="J35" s="138"/>
-      <c r="K35" s="138"/>
-      <c r="L35" s="138" t="s">
-        <v>10</v>
-      </c>
-      <c r="M35" s="138"/>
-      <c r="N35" s="138"/>
-      <c r="O35" s="138"/>
-      <c r="P35" s="138"/>
-      <c r="Q35" s="138"/>
-      <c r="R35" s="138"/>
-      <c r="S35" s="23"/>
-    </row>
-    <row r="36" spans="1:19" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="34"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="39"/>
-      <c r="M36" s="39"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="39"/>
-      <c r="Q36" s="39"/>
-      <c r="R36" s="39"/>
-      <c r="S36" s="24"/>
-    </row>
-    <row r="37" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="34"/>
-      <c r="B37" s="35"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="39"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="35"/>
-      <c r="L37" s="89" t="s">
-        <v>12</v>
-      </c>
-      <c r="M37" s="76"/>
-      <c r="N37" s="76"/>
-      <c r="O37" s="130"/>
-      <c r="P37" s="130"/>
-      <c r="Q37" s="130"/>
-      <c r="R37" s="131"/>
-      <c r="S37" s="142"/>
-    </row>
-    <row r="38" spans="1:19" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A38" s="77"/>
-      <c r="B38" s="78"/>
-      <c r="C38" s="78"/>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="79"/>
-      <c r="J38" s="79"/>
-      <c r="K38" s="78"/>
-      <c r="L38" s="97" t="s">
-        <v>44</v>
-      </c>
-      <c r="M38" s="98"/>
-      <c r="N38" s="98"/>
-      <c r="O38" s="95"/>
-      <c r="P38" s="95"/>
-      <c r="Q38" s="95"/>
-      <c r="R38" s="96"/>
-      <c r="S38" s="143"/>
-    </row>
-    <row r="39" spans="1:19" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="34"/>
-      <c r="B39" s="80"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="35"/>
-      <c r="L39" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="M39" s="82"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="132"/>
-      <c r="P39" s="132"/>
-      <c r="Q39" s="132"/>
-      <c r="R39" s="133"/>
-      <c r="S39" s="144"/>
-    </row>
-    <row r="40" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="34"/>
-      <c r="B40" s="84"/>
-      <c r="C40" s="85"/>
-      <c r="D40" s="85"/>
-      <c r="E40" s="85"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="39"/>
-      <c r="K40" s="39"/>
-      <c r="L40" s="39"/>
-      <c r="M40" s="39"/>
-      <c r="N40" s="39"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="39"/>
-      <c r="Q40" s="39"/>
-      <c r="R40" s="39"/>
-      <c r="S40" s="24"/>
-    </row>
-    <row r="41" spans="1:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="34"/>
-      <c r="B41" s="86" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41" s="87"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="87"/>
-      <c r="G41" s="140"/>
-      <c r="H41" s="140"/>
-      <c r="I41" s="140"/>
-      <c r="J41" s="140"/>
-      <c r="K41" s="35"/>
-      <c r="L41" s="84"/>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="39"/>
-      <c r="P41" s="39"/>
-      <c r="Q41" s="39"/>
-      <c r="R41" s="39"/>
-      <c r="S41" s="24"/>
-    </row>
-    <row r="42" spans="1:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="34"/>
-      <c r="B42" s="139" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="139"/>
-      <c r="D42" s="139"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="139"/>
-      <c r="H42" s="139"/>
-      <c r="I42" s="139"/>
-      <c r="J42" s="139"/>
-      <c r="K42" s="139"/>
-      <c r="L42" s="84"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
-      <c r="P42" s="39"/>
-      <c r="Q42" s="39"/>
-      <c r="R42" s="39"/>
+      <c r="C42" s="104"/>
+      <c r="D42" s="104"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="104"/>
+      <c r="K42" s="104"/>
+      <c r="L42" s="86"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="42"/>
+      <c r="R42" s="42"/>
       <c r="S42" s="24"/>
     </row>
-    <row r="43" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="88"/>
-      <c r="B43" s="135" t="s">
+    <row r="43" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="90"/>
+      <c r="B43" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="135"/>
-      <c r="D43" s="135"/>
-      <c r="E43" s="135"/>
-      <c r="F43" s="135"/>
-      <c r="G43" s="135"/>
-      <c r="H43" s="135"/>
-      <c r="I43" s="135"/>
-      <c r="J43" s="135"/>
-      <c r="K43" s="135"/>
-      <c r="L43" s="135"/>
-      <c r="M43" s="135"/>
-      <c r="N43" s="135"/>
-      <c r="O43" s="135"/>
-      <c r="P43" s="135"/>
-      <c r="Q43" s="135"/>
-      <c r="R43" s="135"/>
-      <c r="S43" s="25"/>
-    </row>
-    <row r="44" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="35"/>
-      <c r="B44" s="136" t="s">
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="99"/>
+      <c r="N43" s="99"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="99"/>
+      <c r="R43" s="99"/>
+      <c r="S43" s="28"/>
+    </row>
+    <row r="44" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="38"/>
+      <c r="B44" s="100" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="136"/>
-      <c r="D44" s="136"/>
-      <c r="E44" s="136"/>
-      <c r="F44" s="136"/>
-      <c r="G44" s="136"/>
-      <c r="H44" s="136"/>
-      <c r="I44" s="136"/>
-      <c r="J44" s="136"/>
-      <c r="K44" s="136"/>
-      <c r="L44" s="136"/>
-      <c r="M44" s="136"/>
-      <c r="N44" s="136"/>
-      <c r="O44" s="136"/>
-      <c r="P44" s="136"/>
-      <c r="Q44" s="136"/>
-      <c r="R44" s="136"/>
+      <c r="C44" s="100"/>
+      <c r="D44" s="100"/>
+      <c r="E44" s="100"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="100"/>
+      <c r="H44" s="100"/>
+      <c r="I44" s="100"/>
+      <c r="J44" s="100"/>
+      <c r="K44" s="100"/>
+      <c r="L44" s="100"/>
+      <c r="M44" s="100"/>
+      <c r="N44" s="100"/>
+      <c r="O44" s="100"/>
+      <c r="P44" s="100"/>
+      <c r="Q44" s="100"/>
+      <c r="R44" s="100"/>
       <c r="S44" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="F5:N5"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="F11:R11"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:O7"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="F3:M3"/>
+    <mergeCell ref="F9:R9"/>
+    <mergeCell ref="F10:R10"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="E19:R19"/>
+    <mergeCell ref="C27:I27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="G31:R31"/>
     <mergeCell ref="O37:R37"/>
     <mergeCell ref="O39:R39"/>
     <mergeCell ref="F4:M4"/>
@@ -3387,47 +3425,6 @@
     <mergeCell ref="H34:K34"/>
     <mergeCell ref="H35:K35"/>
     <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="G31:R31"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="E19:R19"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="F11:R11"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:O7"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="F3:M3"/>
-    <mergeCell ref="F9:R9"/>
-    <mergeCell ref="F10:R10"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q26:R26"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_111_VAT INVOICE_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_111_VAT INVOICE_IMP.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\GENUWIN\19. Package\98. 2205 WABOOK\1.2307 WeTAX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAP-DEV-06\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5916"/>
   </bookViews>
   <sheets>
-    <sheet name="Invoice" sheetId="4" r:id="rId1"/>
+    <sheet name="Invoice" sheetId="5" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -78,9 +78,6 @@
     <t>6 = 4 x 5</t>
   </si>
   <si>
-    <t xml:space="preserve">MCCQT: </t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Người mua hàng / </t>
     </r>
@@ -333,71 +330,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Ngày /</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Date</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> tháng / </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>month</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">    năm /</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>year</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">    </t>
-    </r>
-  </si>
-  <si>
     <t>VAT INVOICE</t>
   </si>
   <si>
@@ -670,12 +602,71 @@
       </rPr>
       <t xml:space="preserve">: </t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ngày / </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Date   </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> tháng / </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>month</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">    năm / </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>year</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">    </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="54" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -966,13 +957,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
@@ -1004,22 +988,25 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
+      <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <i/>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1112,8 +1099,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="36">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -1512,6 +1505,15 @@
       <bottom style="medium">
         <color rgb="FF0070C0"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1700,9 +1702,6 @@
     <xf numFmtId="0" fontId="45" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1724,20 +1723,11 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1751,13 +1741,7 @@
     <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1800,34 +1784,88 @@
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="46" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="46" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="46" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1835,20 +1873,17 @@
     <xf numFmtId="0" fontId="31" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="47" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="47" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1856,14 +1891,17 @@
     <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
@@ -1871,24 +1909,39 @@
     <xf numFmtId="49" fontId="7" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1901,80 +1954,29 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="26" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="26" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2298,31 +2300,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.5546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="1.6640625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="5.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="1.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="4.33203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="0.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.6640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="4.6640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="0.6640625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.6640625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="1.6640625" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.33203125" style="1"/>
+    <col min="4" max="4" width="1.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="1.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="0.6640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="0.6640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="14.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="1.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="4.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32"/>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -2341,109 +2346,119 @@
       <c r="P1" s="32"/>
       <c r="Q1" s="32"/>
       <c r="R1" s="32"/>
-    </row>
-    <row r="2" spans="1:19" ht="25.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+    </row>
+    <row r="2" spans="1:21" ht="25.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33"/>
       <c r="B2" s="34"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
       <c r="E2" s="35"/>
-      <c r="F2" s="129" t="s">
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="124" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="124"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="11"/>
-    </row>
-    <row r="3" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="139" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="139"/>
+      <c r="R2" s="139"/>
+      <c r="S2" s="139"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="11"/>
+    </row>
+    <row r="3" spans="1:21" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37"/>
       <c r="B3" s="38"/>
       <c r="C3" s="38"/>
       <c r="D3" s="38"/>
       <c r="E3" s="38"/>
-      <c r="F3" s="130" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="125" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" s="125"/>
-      <c r="P3" s="125"/>
-      <c r="Q3" s="125"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="12"/>
-    </row>
-    <row r="4" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="140" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="140"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="140"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="140"/>
+      <c r="P3" s="141" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q3" s="141"/>
+      <c r="R3" s="141"/>
+      <c r="S3" s="141"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="12"/>
+    </row>
+    <row r="4" spans="1:21" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37"/>
       <c r="B4" s="38"/>
       <c r="C4" s="38"/>
       <c r="D4" s="38"/>
       <c r="E4" s="38"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
       <c r="P4" s="40"/>
       <c r="Q4" s="40"/>
       <c r="R4" s="40"/>
-      <c r="S4" s="12"/>
-    </row>
-    <row r="5" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="12"/>
+    </row>
+    <row r="5" spans="1:21" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37"/>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
       <c r="D5" s="38"/>
       <c r="E5" s="38"/>
-      <c r="F5" s="128" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="142" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="142"/>
+      <c r="J5" s="142"/>
+      <c r="K5" s="142"/>
+      <c r="L5" s="142"/>
+      <c r="M5" s="142"/>
+      <c r="N5" s="142"/>
       <c r="O5" s="40"/>
       <c r="P5" s="40"/>
       <c r="Q5" s="40"/>
       <c r="R5" s="40"/>
-      <c r="S5" s="13"/>
-    </row>
-    <row r="6" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S5" s="40"/>
+      <c r="T5" s="40"/>
+      <c r="U5" s="13"/>
+    </row>
+    <row r="6" spans="1:21" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="37"/>
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
       <c r="D6" s="38"/>
       <c r="E6" s="38"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
       <c r="H6" s="40"/>
       <c r="I6" s="40"/>
       <c r="J6" s="40"/>
@@ -2455,42 +2470,46 @@
       <c r="P6" s="40"/>
       <c r="Q6" s="40"/>
       <c r="R6" s="40"/>
-      <c r="S6" s="13"/>
-    </row>
-    <row r="7" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="13"/>
+    </row>
+    <row r="7" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37"/>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
-      <c r="D7" s="126" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="127"/>
-      <c r="K7" s="127"/>
-      <c r="L7" s="127"/>
-      <c r="M7" s="127"/>
-      <c r="N7" s="127"/>
-      <c r="O7" s="127"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="76" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="76"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="95"/>
+      <c r="Q7" s="95"/>
       <c r="R7" s="38"/>
-      <c r="S7" s="13"/>
-    </row>
-    <row r="8" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="13"/>
+    </row>
+    <row r="8" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37"/>
       <c r="B8" s="41"/>
       <c r="C8" s="41"/>
       <c r="D8" s="41"/>
       <c r="E8" s="41"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
       <c r="H8" s="42"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
       <c r="K8" s="38"/>
       <c r="L8" s="38"/>
       <c r="M8" s="38"/>
@@ -2499,670 +2518,726 @@
       <c r="P8" s="38"/>
       <c r="Q8" s="38"/>
       <c r="R8" s="38"/>
-      <c r="S8" s="12"/>
-    </row>
-    <row r="9" spans="1:19" ht="25.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="12"/>
+    </row>
+    <row r="9" spans="1:21" ht="25.2" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A9" s="43"/>
       <c r="B9" s="44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="132"/>
-      <c r="J9" s="132"/>
-      <c r="K9" s="132"/>
-      <c r="L9" s="132"/>
-      <c r="M9" s="132"/>
-      <c r="N9" s="132"/>
-      <c r="O9" s="132"/>
-      <c r="P9" s="132"/>
-      <c r="Q9" s="132"/>
-      <c r="R9" s="132"/>
-      <c r="S9" s="14"/>
-    </row>
-    <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="135"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="135"/>
+      <c r="L9" s="135"/>
+      <c r="M9" s="135"/>
+      <c r="N9" s="135"/>
+      <c r="O9" s="135"/>
+      <c r="P9" s="135"/>
+      <c r="Q9" s="135"/>
+      <c r="R9" s="135"/>
+      <c r="S9" s="135"/>
+      <c r="T9" s="135"/>
+      <c r="U9" s="14"/>
+    </row>
+    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37"/>
       <c r="B10" s="41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="38"/>
       <c r="D10" s="38"/>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="131"/>
-      <c r="M10" s="131"/>
-      <c r="N10" s="131"/>
-      <c r="O10" s="131"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="131"/>
-      <c r="S10" s="12"/>
-    </row>
-    <row r="11" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H10" s="136"/>
+      <c r="I10" s="136"/>
+      <c r="J10" s="136"/>
+      <c r="K10" s="136"/>
+      <c r="L10" s="136"/>
+      <c r="M10" s="136"/>
+      <c r="N10" s="136"/>
+      <c r="O10" s="136"/>
+      <c r="P10" s="136"/>
+      <c r="Q10" s="136"/>
+      <c r="R10" s="136"/>
+      <c r="S10" s="136"/>
+      <c r="T10" s="136"/>
+      <c r="U10" s="12"/>
+    </row>
+    <row r="11" spans="1:21" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37"/>
       <c r="B11" s="41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="119"/>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="119"/>
-      <c r="K11" s="119"/>
-      <c r="L11" s="119"/>
-      <c r="M11" s="119"/>
-      <c r="N11" s="119"/>
-      <c r="O11" s="119"/>
-      <c r="P11" s="119"/>
-      <c r="Q11" s="119"/>
-      <c r="R11" s="119"/>
-      <c r="S11" s="12"/>
-    </row>
-    <row r="12" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="137"/>
+      <c r="S11" s="137"/>
+      <c r="T11" s="137"/>
+      <c r="U11" s="12"/>
+    </row>
+    <row r="12" spans="1:21" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
       <c r="B12" s="46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="38"/>
       <c r="D12" s="38"/>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="115"/>
-      <c r="G12" s="115"/>
-      <c r="H12" s="115"/>
-      <c r="I12" s="115"/>
-      <c r="J12" s="115"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="132"/>
+      <c r="K12" s="132"/>
+      <c r="L12" s="132"/>
       <c r="M12" s="42"/>
       <c r="N12" s="42"/>
-      <c r="O12" s="41"/>
+      <c r="O12" s="42"/>
       <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
+      <c r="Q12" s="41"/>
       <c r="R12" s="42"/>
-      <c r="S12" s="13"/>
-    </row>
-    <row r="13" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S12" s="42"/>
+      <c r="T12" s="42"/>
+      <c r="U12" s="13"/>
+    </row>
+    <row r="13" spans="1:21" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37"/>
       <c r="B13" s="46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" s="38"/>
       <c r="D13" s="38"/>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="115"/>
-      <c r="K13" s="115"/>
-      <c r="L13" s="115"/>
-      <c r="M13" s="115"/>
-      <c r="N13" s="115"/>
-      <c r="O13" s="115"/>
-      <c r="P13" s="115"/>
-      <c r="Q13" s="115"/>
-      <c r="R13" s="115"/>
-      <c r="S13" s="13"/>
-    </row>
-    <row r="14" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
+      <c r="M13" s="132"/>
+      <c r="N13" s="132"/>
+      <c r="O13" s="132"/>
+      <c r="P13" s="132"/>
+      <c r="Q13" s="132"/>
+      <c r="R13" s="132"/>
+      <c r="S13" s="132"/>
+      <c r="T13" s="132"/>
+      <c r="U13" s="13"/>
+    </row>
+    <row r="14" spans="1:21" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37"/>
       <c r="B14" s="38"/>
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="116"/>
-      <c r="H14" s="116"/>
-      <c r="I14" s="116"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="116"/>
-      <c r="L14" s="116"/>
-      <c r="M14" s="116"/>
-      <c r="N14" s="116"/>
-      <c r="O14" s="116"/>
-      <c r="P14" s="116"/>
-      <c r="Q14" s="116"/>
-      <c r="R14" s="116"/>
-      <c r="S14" s="13"/>
-    </row>
-    <row r="15" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="133"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="133"/>
+      <c r="N14" s="133"/>
+      <c r="O14" s="133"/>
+      <c r="P14" s="133"/>
+      <c r="Q14" s="133"/>
+      <c r="R14" s="133"/>
+      <c r="S14" s="133"/>
+      <c r="T14" s="133"/>
+      <c r="U14" s="13"/>
+    </row>
+    <row r="15" spans="1:21" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37"/>
       <c r="B15" s="47"/>
       <c r="C15" s="47"/>
       <c r="D15" s="47"/>
       <c r="E15" s="47"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="49"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="49"/>
-      <c r="R15" s="49"/>
-      <c r="S15" s="13"/>
-    </row>
-    <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="89"/>
+      <c r="M15" s="89"/>
+      <c r="N15" s="89"/>
+      <c r="O15" s="89"/>
+      <c r="P15" s="89"/>
+      <c r="Q15" s="89"/>
+      <c r="R15" s="89"/>
+      <c r="S15" s="89"/>
+      <c r="T15" s="89"/>
+      <c r="U15" s="13"/>
+    </row>
+    <row r="16" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
       <c r="B16" s="41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="41"/>
       <c r="D16" s="41"/>
       <c r="E16" s="41"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="51"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="51"/>
-      <c r="S16" s="29"/>
-    </row>
-    <row r="17" spans="1:19" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="50"/>
+      <c r="L16" s="50"/>
+      <c r="M16" s="50"/>
+      <c r="N16" s="50"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="50"/>
+      <c r="R16" s="50"/>
+      <c r="S16" s="50"/>
+      <c r="T16" s="50"/>
+      <c r="U16" s="29"/>
+    </row>
+    <row r="17" spans="1:21" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="37"/>
       <c r="B17" s="41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
       <c r="E17" s="41"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
-      <c r="K17" s="52"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="52"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="52"/>
-      <c r="S17" s="15"/>
-    </row>
-    <row r="18" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I17" s="49"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+      <c r="L17" s="51"/>
+      <c r="M17" s="51"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="51"/>
+      <c r="P17" s="51"/>
+      <c r="Q17" s="51"/>
+      <c r="R17" s="51"/>
+      <c r="S17" s="51"/>
+      <c r="T17" s="51"/>
+      <c r="U17" s="15"/>
+    </row>
+    <row r="18" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="37"/>
       <c r="B18" s="41" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="41"/>
       <c r="E18" s="41"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="53"/>
-      <c r="Q18" s="53"/>
-      <c r="R18" s="53"/>
-      <c r="S18" s="15"/>
-    </row>
-    <row r="19" spans="1:19" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="52"/>
+      <c r="P18" s="52"/>
+      <c r="Q18" s="52"/>
+      <c r="R18" s="52"/>
+      <c r="S18" s="52"/>
+      <c r="T18" s="52"/>
+      <c r="U18" s="15"/>
+    </row>
+    <row r="19" spans="1:21" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="37"/>
       <c r="B19" s="41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" s="41"/>
-      <c r="D19" s="93"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="119"/>
-      <c r="J19" s="119"/>
-      <c r="K19" s="119"/>
-      <c r="L19" s="119"/>
-      <c r="M19" s="119"/>
-      <c r="N19" s="119"/>
-      <c r="O19" s="119"/>
-      <c r="P19" s="119"/>
-      <c r="Q19" s="119"/>
-      <c r="R19" s="119"/>
-      <c r="S19" s="15"/>
-    </row>
-    <row r="20" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="41"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="132"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="132"/>
+      <c r="J19" s="132"/>
+      <c r="K19" s="132"/>
+      <c r="L19" s="132"/>
+      <c r="M19" s="132"/>
+      <c r="N19" s="132"/>
+      <c r="O19" s="132"/>
+      <c r="P19" s="132"/>
+      <c r="Q19" s="132"/>
+      <c r="R19" s="132"/>
+      <c r="S19" s="132"/>
+      <c r="T19" s="132"/>
+      <c r="U19" s="15"/>
+    </row>
+    <row r="20" spans="1:21" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="37"/>
       <c r="B20" s="41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C20" s="41"/>
       <c r="D20" s="41"/>
       <c r="E20" s="41"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="15"/>
-    </row>
-    <row r="21" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="52"/>
+      <c r="K20" s="52"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="52"/>
+      <c r="O20" s="52"/>
+      <c r="P20" s="52"/>
+      <c r="Q20" s="52"/>
+      <c r="R20" s="52"/>
+      <c r="S20" s="52"/>
+      <c r="T20" s="52"/>
+      <c r="U20" s="15"/>
+    </row>
+    <row r="21" spans="1:21" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="37"/>
       <c r="B21" s="41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="41"/>
       <c r="D21" s="41"/>
       <c r="E21" s="41"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
       <c r="H21" s="38"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="104"/>
+      <c r="K21" s="104"/>
+      <c r="L21" s="104"/>
       <c r="M21" s="38"/>
       <c r="N21" s="38"/>
       <c r="O21" s="38"/>
       <c r="P21" s="38"/>
       <c r="Q21" s="38"/>
       <c r="R21" s="38"/>
-      <c r="S21" s="12"/>
-    </row>
-    <row r="22" spans="1:19" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="12"/>
+    </row>
+    <row r="22" spans="1:21" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="37"/>
       <c r="B22" s="41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
       <c r="H22" s="38"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="38" t="s">
+        <v>21</v>
+      </c>
       <c r="N22" s="38"/>
       <c r="O22" s="38"/>
       <c r="P22" s="38"/>
       <c r="Q22" s="38"/>
       <c r="R22" s="38"/>
-      <c r="S22" s="12"/>
-    </row>
-    <row r="23" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S22" s="38"/>
+      <c r="T22" s="38"/>
+      <c r="U22" s="12"/>
+    </row>
+    <row r="23" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="37"/>
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
       <c r="E23" s="41"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
       <c r="H23" s="38"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="41"/>
       <c r="M23" s="38"/>
       <c r="N23" s="38"/>
       <c r="O23" s="38"/>
       <c r="P23" s="38"/>
       <c r="Q23" s="38"/>
       <c r="R23" s="38"/>
-      <c r="S23" s="12"/>
-    </row>
-    <row r="24" spans="1:19" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A24" s="55"/>
-      <c r="B24" s="56" t="s">
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="12"/>
+    </row>
+    <row r="24" spans="1:21" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A24" s="54"/>
+      <c r="B24" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="117" t="s">
+      <c r="C24" s="134" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="117"/>
-      <c r="I24" s="117"/>
-      <c r="J24" s="57" t="s">
-        <v>33</v>
-      </c>
-      <c r="K24" s="117" t="s">
+      <c r="D24" s="134"/>
+      <c r="E24" s="134"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="134"/>
+      <c r="J24" s="134"/>
+      <c r="K24" s="134"/>
+      <c r="L24" s="84" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" s="134" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="117"/>
-      <c r="M24" s="117"/>
-      <c r="N24" s="117" t="s">
+      <c r="N24" s="134"/>
+      <c r="O24" s="134"/>
+      <c r="P24" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="117"/>
-      <c r="P24" s="117"/>
-      <c r="Q24" s="117" t="s">
+      <c r="Q24" s="134"/>
+      <c r="R24" s="134"/>
+      <c r="S24" s="134" t="s">
         <v>7</v>
       </c>
-      <c r="R24" s="117"/>
-      <c r="S24" s="16"/>
-    </row>
-    <row r="25" spans="1:19" s="4" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="58"/>
-      <c r="B25" s="59" t="s">
+      <c r="T24" s="134"/>
+      <c r="U24" s="16"/>
+    </row>
+    <row r="25" spans="1:21" s="4" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="56"/>
+      <c r="B25" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="118" t="s">
+      <c r="C25" s="130" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="118"/>
-      <c r="G25" s="118"/>
-      <c r="H25" s="118"/>
-      <c r="I25" s="118"/>
-      <c r="J25" s="59" t="s">
+      <c r="D25" s="130"/>
+      <c r="E25" s="130"/>
+      <c r="F25" s="130"/>
+      <c r="G25" s="130"/>
+      <c r="H25" s="130"/>
+      <c r="I25" s="130"/>
+      <c r="J25" s="130"/>
+      <c r="K25" s="130"/>
+      <c r="L25" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="K25" s="118" t="s">
+      <c r="M25" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="L25" s="118"/>
-      <c r="M25" s="118"/>
-      <c r="N25" s="118" t="s">
+      <c r="N25" s="130"/>
+      <c r="O25" s="130"/>
+      <c r="P25" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="O25" s="118"/>
-      <c r="P25" s="118"/>
-      <c r="Q25" s="118" t="s">
+      <c r="Q25" s="130"/>
+      <c r="R25" s="130"/>
+      <c r="S25" s="130" t="s">
         <v>8</v>
       </c>
-      <c r="R25" s="118"/>
-      <c r="S25" s="17"/>
-    </row>
-    <row r="26" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="60"/>
-      <c r="B26" s="61">
+      <c r="T25" s="130"/>
+      <c r="U25" s="17"/>
+    </row>
+    <row r="26" spans="1:21" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="57"/>
+      <c r="B26" s="86">
         <v>1</v>
       </c>
-      <c r="C26" s="114">
+      <c r="C26" s="131">
         <v>2</v>
       </c>
-      <c r="D26" s="114"/>
-      <c r="E26" s="114"/>
-      <c r="F26" s="114"/>
-      <c r="G26" s="114"/>
-      <c r="H26" s="114"/>
-      <c r="I26" s="114"/>
-      <c r="J26" s="61">
+      <c r="D26" s="131"/>
+      <c r="E26" s="131"/>
+      <c r="F26" s="131"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="131"/>
+      <c r="I26" s="131"/>
+      <c r="J26" s="131"/>
+      <c r="K26" s="131"/>
+      <c r="L26" s="86">
         <v>3</v>
       </c>
-      <c r="K26" s="114">
+      <c r="M26" s="131">
         <v>4</v>
       </c>
-      <c r="L26" s="114"/>
-      <c r="M26" s="114"/>
-      <c r="N26" s="114">
+      <c r="N26" s="131"/>
+      <c r="O26" s="131"/>
+      <c r="P26" s="131">
         <v>5</v>
       </c>
-      <c r="O26" s="114"/>
-      <c r="P26" s="114"/>
-      <c r="Q26" s="114" t="s">
+      <c r="Q26" s="131"/>
+      <c r="R26" s="131"/>
+      <c r="S26" s="131" t="s">
         <v>18</v>
       </c>
-      <c r="R26" s="114"/>
-      <c r="S26" s="18"/>
-    </row>
-    <row r="27" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="62"/>
-      <c r="B27" s="133"/>
-      <c r="C27" s="134"/>
-      <c r="D27" s="135"/>
-      <c r="E27" s="135"/>
-      <c r="F27" s="135"/>
-      <c r="G27" s="135"/>
-      <c r="H27" s="135"/>
-      <c r="I27" s="136"/>
-      <c r="J27" s="137"/>
-      <c r="K27" s="138"/>
-      <c r="L27" s="139"/>
-      <c r="M27" s="140"/>
-      <c r="N27" s="138"/>
-      <c r="O27" s="139"/>
-      <c r="P27" s="140"/>
-      <c r="Q27" s="141"/>
-      <c r="R27" s="142"/>
-      <c r="S27" s="30"/>
-    </row>
-    <row r="28" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="62"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="64"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="65"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="110" t="s">
+      <c r="T26" s="131"/>
+      <c r="U26" s="18"/>
+    </row>
+    <row r="27" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="58"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="122"/>
+      <c r="D27" s="123"/>
+      <c r="E27" s="123"/>
+      <c r="F27" s="123"/>
+      <c r="G27" s="123"/>
+      <c r="H27" s="123"/>
+      <c r="I27" s="123"/>
+      <c r="J27" s="123"/>
+      <c r="K27" s="124"/>
+      <c r="L27" s="91"/>
+      <c r="M27" s="125"/>
+      <c r="N27" s="126"/>
+      <c r="O27" s="127"/>
+      <c r="P27" s="125"/>
+      <c r="Q27" s="126"/>
+      <c r="R27" s="127"/>
+      <c r="S27" s="128"/>
+      <c r="T27" s="129"/>
+      <c r="U27" s="30"/>
+    </row>
+    <row r="28" spans="1:21" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="58"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+      <c r="J28" s="61"/>
+      <c r="K28" s="61"/>
+      <c r="L28" s="116" t="s">
+        <v>40</v>
+      </c>
+      <c r="M28" s="116"/>
+      <c r="N28" s="116"/>
+      <c r="O28" s="116"/>
+      <c r="P28" s="116"/>
+      <c r="Q28" s="116"/>
+      <c r="R28" s="117"/>
+      <c r="S28" s="118"/>
+      <c r="T28" s="119"/>
+      <c r="U28" s="31"/>
+    </row>
+    <row r="29" spans="1:21" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="58"/>
+      <c r="B29" s="114" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="115"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="88"/>
+      <c r="L29" s="116" t="s">
+        <v>41</v>
+      </c>
+      <c r="M29" s="116"/>
+      <c r="N29" s="116"/>
+      <c r="O29" s="116"/>
+      <c r="P29" s="116"/>
+      <c r="Q29" s="116"/>
+      <c r="R29" s="117"/>
+      <c r="S29" s="118"/>
+      <c r="T29" s="119"/>
+      <c r="U29" s="31"/>
+    </row>
+    <row r="30" spans="1:21" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="58"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="88"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="88"/>
+      <c r="I30" s="88"/>
+      <c r="J30" s="88"/>
+      <c r="K30" s="88"/>
+      <c r="L30" s="116" t="s">
         <v>42</v>
       </c>
-      <c r="K28" s="110"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="110"/>
-      <c r="N28" s="110"/>
-      <c r="O28" s="110"/>
-      <c r="P28" s="111"/>
-      <c r="Q28" s="106"/>
-      <c r="R28" s="107"/>
-      <c r="S28" s="31"/>
-    </row>
-    <row r="29" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="62"/>
-      <c r="B29" s="108" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="109"/>
-      <c r="D29" s="109"/>
-      <c r="E29" s="109"/>
-      <c r="F29" s="109"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="110" t="s">
-        <v>43</v>
-      </c>
-      <c r="K29" s="110"/>
-      <c r="L29" s="110"/>
-      <c r="M29" s="110"/>
-      <c r="N29" s="110"/>
-      <c r="O29" s="110"/>
-      <c r="P29" s="111"/>
-      <c r="Q29" s="106"/>
-      <c r="R29" s="107"/>
-      <c r="S29" s="31"/>
-    </row>
-    <row r="30" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="62"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="110" t="s">
-        <v>44</v>
-      </c>
-      <c r="K30" s="110"/>
-      <c r="L30" s="110"/>
-      <c r="M30" s="110"/>
-      <c r="N30" s="110"/>
-      <c r="O30" s="110"/>
-      <c r="P30" s="111"/>
-      <c r="Q30" s="106"/>
-      <c r="R30" s="107"/>
-      <c r="S30" s="31"/>
-    </row>
-    <row r="31" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="55"/>
-      <c r="B31" s="92" t="s">
-        <v>48</v>
+      <c r="M30" s="116"/>
+      <c r="N30" s="116"/>
+      <c r="O30" s="116"/>
+      <c r="P30" s="116"/>
+      <c r="Q30" s="116"/>
+      <c r="R30" s="117"/>
+      <c r="S30" s="118"/>
+      <c r="T30" s="119"/>
+      <c r="U30" s="31"/>
+    </row>
+    <row r="31" spans="1:21" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="54"/>
+      <c r="B31" s="83" t="s">
+        <v>46</v>
       </c>
       <c r="C31" s="44"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
       <c r="F31" s="44"/>
-      <c r="G31" s="112"/>
-      <c r="H31" s="112"/>
-      <c r="I31" s="112"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="112"/>
-      <c r="L31" s="112"/>
-      <c r="M31" s="112"/>
-      <c r="N31" s="112"/>
-      <c r="O31" s="112"/>
-      <c r="P31" s="112"/>
-      <c r="Q31" s="112"/>
-      <c r="R31" s="113"/>
-      <c r="S31" s="19"/>
-    </row>
-    <row r="32" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="120"/>
+      <c r="L31" s="120"/>
+      <c r="M31" s="120"/>
+      <c r="N31" s="120"/>
+      <c r="O31" s="120"/>
+      <c r="P31" s="120"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="120"/>
+      <c r="S31" s="120"/>
+      <c r="T31" s="121"/>
+      <c r="U31" s="19"/>
+    </row>
+    <row r="32" spans="1:21" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="37"/>
-      <c r="B32" s="69"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="71"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="71"/>
-      <c r="O32" s="71"/>
-      <c r="P32" s="71"/>
-      <c r="Q32" s="71"/>
-      <c r="R32" s="72"/>
-      <c r="S32" s="20"/>
-    </row>
-    <row r="33" spans="1:19" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="73"/>
-      <c r="B33" s="74"/>
-      <c r="C33" s="101" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="101"/>
-      <c r="H33" s="101"/>
-      <c r="I33" s="101"/>
-      <c r="J33" s="101"/>
-      <c r="K33" s="101"/>
-      <c r="L33" s="101" t="s">
-        <v>39</v>
-      </c>
-      <c r="M33" s="101"/>
-      <c r="N33" s="101"/>
-      <c r="O33" s="101"/>
-      <c r="P33" s="101"/>
-      <c r="Q33" s="101"/>
-      <c r="R33" s="101"/>
-      <c r="S33" s="21"/>
-    </row>
-    <row r="34" spans="1:19" s="8" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="75"/>
-      <c r="B34" s="76"/>
-      <c r="C34" s="102" t="s">
+      <c r="B32" s="63"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="65"/>
+      <c r="L32" s="65"/>
+      <c r="M32" s="65"/>
+      <c r="N32" s="65"/>
+      <c r="O32" s="65"/>
+      <c r="P32" s="65"/>
+      <c r="Q32" s="65"/>
+      <c r="R32" s="65"/>
+      <c r="S32" s="65"/>
+      <c r="T32" s="66"/>
+      <c r="U32" s="20"/>
+    </row>
+    <row r="33" spans="1:21" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="67"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="112" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="112"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="112"/>
+      <c r="H33" s="112"/>
+      <c r="I33" s="112"/>
+      <c r="J33" s="112"/>
+      <c r="K33" s="112"/>
+      <c r="L33" s="112"/>
+      <c r="M33" s="112"/>
+      <c r="N33" s="112" t="s">
+        <v>37</v>
+      </c>
+      <c r="O33" s="112"/>
+      <c r="P33" s="112"/>
+      <c r="Q33" s="112"/>
+      <c r="R33" s="112"/>
+      <c r="S33" s="112"/>
+      <c r="T33" s="112"/>
+      <c r="U33" s="21"/>
+    </row>
+    <row r="34" spans="1:21" s="8" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="69"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="102"/>
-      <c r="E34" s="102"/>
-      <c r="F34" s="102"/>
-      <c r="G34" s="102"/>
-      <c r="H34" s="102"/>
-      <c r="I34" s="102"/>
-      <c r="J34" s="102"/>
-      <c r="K34" s="102"/>
-      <c r="L34" s="102" t="s">
+      <c r="D34" s="113"/>
+      <c r="E34" s="113"/>
+      <c r="F34" s="113"/>
+      <c r="G34" s="113"/>
+      <c r="H34" s="113"/>
+      <c r="I34" s="113"/>
+      <c r="J34" s="113"/>
+      <c r="K34" s="113"/>
+      <c r="L34" s="113"/>
+      <c r="M34" s="113"/>
+      <c r="N34" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="M34" s="102"/>
-      <c r="N34" s="102"/>
-      <c r="O34" s="102"/>
-      <c r="P34" s="102"/>
-      <c r="Q34" s="102"/>
-      <c r="R34" s="102"/>
-      <c r="S34" s="22"/>
-    </row>
-    <row r="35" spans="1:19" s="9" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="58"/>
-      <c r="B35" s="77"/>
-      <c r="C35" s="103" t="s">
+      <c r="O34" s="113"/>
+      <c r="P34" s="113"/>
+      <c r="Q34" s="113"/>
+      <c r="R34" s="113"/>
+      <c r="S34" s="113"/>
+      <c r="T34" s="113"/>
+      <c r="U34" s="22"/>
+    </row>
+    <row r="35" spans="1:21" s="9" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="56"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="103"/>
-      <c r="J35" s="103"/>
-      <c r="K35" s="103"/>
-      <c r="L35" s="103" t="s">
+      <c r="D35" s="105"/>
+      <c r="E35" s="105"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="105"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="105"/>
+      <c r="J35" s="105"/>
+      <c r="K35" s="105"/>
+      <c r="L35" s="105"/>
+      <c r="M35" s="105"/>
+      <c r="N35" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="M35" s="103"/>
-      <c r="N35" s="103"/>
-      <c r="O35" s="103"/>
-      <c r="P35" s="103"/>
-      <c r="Q35" s="103"/>
-      <c r="R35" s="103"/>
-      <c r="S35" s="23"/>
-    </row>
-    <row r="36" spans="1:19" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O35" s="105"/>
+      <c r="P35" s="105"/>
+      <c r="Q35" s="105"/>
+      <c r="R35" s="105"/>
+      <c r="S35" s="105"/>
+      <c r="T35" s="105"/>
+      <c r="U35" s="23"/>
+    </row>
+    <row r="36" spans="1:21" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="37"/>
       <c r="B36" s="42"/>
       <c r="C36" s="42"/>
@@ -3181,85 +3256,93 @@
       <c r="P36" s="42"/>
       <c r="Q36" s="42"/>
       <c r="R36" s="42"/>
-      <c r="S36" s="24"/>
-    </row>
-    <row r="37" spans="1:19" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="S36" s="42"/>
+      <c r="T36" s="42"/>
+      <c r="U36" s="24"/>
+    </row>
+    <row r="37" spans="1:21" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37"/>
       <c r="B37" s="38"/>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
       <c r="E37" s="38"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="42"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
       <c r="H37" s="42"/>
       <c r="I37" s="42"/>
       <c r="J37" s="42"/>
-      <c r="K37" s="38"/>
-      <c r="L37" s="91" t="s">
+      <c r="K37" s="42"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="M37" s="78"/>
-      <c r="N37" s="78"/>
-      <c r="O37" s="94"/>
-      <c r="P37" s="94"/>
-      <c r="Q37" s="94"/>
-      <c r="R37" s="95"/>
-      <c r="S37" s="25"/>
-    </row>
-    <row r="38" spans="1:19" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A38" s="79"/>
-      <c r="B38" s="80"/>
-      <c r="C38" s="80"/>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="81"/>
-      <c r="G38" s="81"/>
-      <c r="H38" s="81"/>
-      <c r="I38" s="81"/>
-      <c r="J38" s="81"/>
-      <c r="K38" s="80"/>
-      <c r="L38" s="122" t="s">
-        <v>45</v>
-      </c>
-      <c r="M38" s="123"/>
-      <c r="N38" s="123"/>
-      <c r="O38" s="120"/>
-      <c r="P38" s="120"/>
-      <c r="Q38" s="120"/>
-      <c r="R38" s="121"/>
-      <c r="S38" s="26"/>
-    </row>
-    <row r="39" spans="1:19" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O37" s="72"/>
+      <c r="P37" s="72"/>
+      <c r="Q37" s="106"/>
+      <c r="R37" s="106"/>
+      <c r="S37" s="106"/>
+      <c r="T37" s="107"/>
+      <c r="U37" s="25"/>
+    </row>
+    <row r="38" spans="1:21" s="10" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="73"/>
+      <c r="B38" s="74"/>
+      <c r="C38" s="74"/>
+      <c r="D38" s="74"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="74"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="75"/>
+      <c r="J38" s="75"/>
+      <c r="K38" s="75"/>
+      <c r="L38" s="75"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="108" t="s">
+        <v>43</v>
+      </c>
+      <c r="O38" s="109"/>
+      <c r="P38" s="109"/>
+      <c r="Q38" s="110"/>
+      <c r="R38" s="110"/>
+      <c r="S38" s="110"/>
+      <c r="T38" s="111"/>
+      <c r="U38" s="26"/>
+    </row>
+    <row r="39" spans="1:21" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="37"/>
-      <c r="B39" s="82"/>
+      <c r="B39" s="76"/>
       <c r="C39" s="38"/>
       <c r="D39" s="38"/>
       <c r="E39" s="38"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
       <c r="H39" s="42"/>
       <c r="I39" s="42"/>
       <c r="J39" s="42"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="83" t="s">
+      <c r="K39" s="42"/>
+      <c r="L39" s="42"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="M39" s="84"/>
-      <c r="N39" s="85"/>
-      <c r="O39" s="96"/>
-      <c r="P39" s="96"/>
-      <c r="Q39" s="96"/>
+      <c r="O39" s="94"/>
+      <c r="P39" s="77"/>
+      <c r="Q39" s="97"/>
       <c r="R39" s="97"/>
-      <c r="S39" s="27"/>
-    </row>
-    <row r="40" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S39" s="97"/>
+      <c r="T39" s="98"/>
+      <c r="U39" s="27"/>
+    </row>
+    <row r="40" spans="1:21" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="37"/>
-      <c r="B40" s="86"/>
-      <c r="C40" s="87"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
+      <c r="B40" s="78"/>
+      <c r="C40" s="79"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="79"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="79"/>
       <c r="H40" s="42"/>
       <c r="I40" s="42"/>
       <c r="J40" s="42"/>
@@ -3271,160 +3354,170 @@
       <c r="P40" s="42"/>
       <c r="Q40" s="42"/>
       <c r="R40" s="42"/>
-      <c r="S40" s="24"/>
-    </row>
-    <row r="41" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S40" s="42"/>
+      <c r="T40" s="42"/>
+      <c r="U40" s="24"/>
+    </row>
+    <row r="41" spans="1:21" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="37"/>
-      <c r="B41" s="88" t="s">
-        <v>37</v>
-      </c>
-      <c r="C41" s="89"/>
-      <c r="D41" s="89"/>
-      <c r="E41" s="89"/>
-      <c r="F41" s="89"/>
-      <c r="G41" s="105"/>
-      <c r="H41" s="105"/>
-      <c r="I41" s="105"/>
-      <c r="J41" s="105"/>
-      <c r="K41" s="38"/>
-      <c r="L41" s="86"/>
-      <c r="M41" s="42"/>
-      <c r="N41" s="42"/>
+      <c r="B41" s="80" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="81"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="99"/>
+      <c r="J41" s="99"/>
+      <c r="K41" s="99"/>
+      <c r="L41" s="99"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="78"/>
       <c r="O41" s="42"/>
       <c r="P41" s="42"/>
       <c r="Q41" s="42"/>
       <c r="R41" s="42"/>
-      <c r="S41" s="24"/>
-    </row>
-    <row r="42" spans="1:19" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S41" s="42"/>
+      <c r="T41" s="42"/>
+      <c r="U41" s="24"/>
+    </row>
+    <row r="42" spans="1:21" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37"/>
-      <c r="B42" s="104" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42" s="104"/>
-      <c r="D42" s="104"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="104"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="104"/>
-      <c r="K42" s="104"/>
-      <c r="L42" s="86"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
+      <c r="B42" s="100" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="100"/>
+      <c r="D42" s="100"/>
+      <c r="E42" s="100"/>
+      <c r="F42" s="100"/>
+      <c r="G42" s="100"/>
+      <c r="H42" s="100"/>
+      <c r="I42" s="100"/>
+      <c r="J42" s="100"/>
+      <c r="K42" s="100"/>
+      <c r="L42" s="100"/>
+      <c r="M42" s="100"/>
+      <c r="N42" s="78"/>
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="42"/>
       <c r="R42" s="42"/>
-      <c r="S42" s="24"/>
-    </row>
-    <row r="43" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="90"/>
-      <c r="B43" s="99" t="s">
+      <c r="S42" s="42"/>
+      <c r="T42" s="42"/>
+      <c r="U42" s="24"/>
+    </row>
+    <row r="43" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="82"/>
+      <c r="B43" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="99"/>
-      <c r="R43" s="99"/>
-      <c r="S43" s="28"/>
-    </row>
-    <row r="44" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="101"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="101"/>
+      <c r="F43" s="101"/>
+      <c r="G43" s="101"/>
+      <c r="H43" s="101"/>
+      <c r="I43" s="101"/>
+      <c r="J43" s="101"/>
+      <c r="K43" s="101"/>
+      <c r="L43" s="101"/>
+      <c r="M43" s="101"/>
+      <c r="N43" s="101"/>
+      <c r="O43" s="101"/>
+      <c r="P43" s="101"/>
+      <c r="Q43" s="101"/>
+      <c r="R43" s="101"/>
+      <c r="S43" s="101"/>
+      <c r="T43" s="101"/>
+      <c r="U43" s="28"/>
+    </row>
+    <row r="44" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="38"/>
-      <c r="B44" s="100" t="s">
-        <v>32</v>
-      </c>
-      <c r="C44" s="100"/>
-      <c r="D44" s="100"/>
-      <c r="E44" s="100"/>
-      <c r="F44" s="100"/>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="100"/>
-      <c r="N44" s="100"/>
-      <c r="O44" s="100"/>
-      <c r="P44" s="100"/>
-      <c r="Q44" s="100"/>
-      <c r="R44" s="100"/>
-      <c r="S44" s="2"/>
+      <c r="B44" s="102" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="102"/>
+      <c r="D44" s="102"/>
+      <c r="E44" s="102"/>
+      <c r="F44" s="102"/>
+      <c r="G44" s="102"/>
+      <c r="H44" s="102"/>
+      <c r="I44" s="102"/>
+      <c r="J44" s="102"/>
+      <c r="K44" s="102"/>
+      <c r="L44" s="102"/>
+      <c r="M44" s="102"/>
+      <c r="N44" s="102"/>
+      <c r="O44" s="102"/>
+      <c r="P44" s="102"/>
+      <c r="Q44" s="102"/>
+      <c r="R44" s="102"/>
+      <c r="S44" s="102"/>
+      <c r="T44" s="102"/>
+      <c r="U44" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="L38:N38"/>
-    <mergeCell ref="F11:R11"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:O7"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="F3:M3"/>
-    <mergeCell ref="F9:R9"/>
-    <mergeCell ref="F10:R10"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="E19:R19"/>
-    <mergeCell ref="C27:I27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="G31:R31"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="O39:R39"/>
-    <mergeCell ref="F4:M4"/>
-    <mergeCell ref="B43:R43"/>
-    <mergeCell ref="B44:R44"/>
-    <mergeCell ref="L33:R33"/>
-    <mergeCell ref="L34:R34"/>
-    <mergeCell ref="L35:R35"/>
-    <mergeCell ref="B42:K42"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H9:T9"/>
+    <mergeCell ref="H10:T10"/>
+    <mergeCell ref="H11:T11"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="H2:O2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="H3:O3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="H4:O4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:T13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:T14"/>
+    <mergeCell ref="C24:K24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="L28:R28"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="C25:K25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="P25:R25"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="C26:K26"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="Q37:T37"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="Q38:T38"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="N33:T33"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="N34:T34"/>
+    <mergeCell ref="H7:O7"/>
+    <mergeCell ref="E19:T19"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="N35:T35"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="L29:R29"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="L30:R30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="I31:T31"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="Q39:T39"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="B42:M42"/>
+    <mergeCell ref="B43:T43"/>
+    <mergeCell ref="B44:T44"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>
